--- a/IH_Loss_Review.xlsx
+++ b/IH_Loss_Review.xlsx
@@ -823,7 +823,7 @@
     <t xml:space="preserve">Contribution % of Total Inhouse</t>
   </si>
   <si>
-    <t xml:space="preserve">RCA &amp; Action Plan</t>
+    <t xml:space="preserve">RCA</t>
   </si>
   <si>
     <t xml:space="preserve">SLP Ticket ID / Mail</t>
@@ -850,11 +850,7 @@
 * Theft-prone SKUs show net loss of ₹16.5K, led by whey ₹15.0K, chargers ₹567 and deos ₹567.
 * DHM adherence gap and SBC completion pending.
 * LSS racks over capacity, pickers unable to locate stock in aisle.
-* SLP theft investigation: ₹15,000 recovery.
-* Clear FCC bin of ₹75.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Isopure Whey Protein Isolate (₹6.2K), Zippo Armor Brushed Chrome (₹5.9K) and TrueBasics Clean Whey Pure Protein (₹5.1K) and match with last GRN qty.
-* W2W audit of aisles O and P as Adjustment is ₹69.3K.
-* Reconcile RTO ₹1.4K with LM and PO cancel ₹9.0K with procurement and DH.</t>
+* SLP theft investigation: ₹15,000 recovery.</t>
   </si>
   <si>
     <t xml:space="preserve">Theft Investigation – Recovery of ₹15,000</t>
@@ -866,11 +862,7 @@
 * Loss is spread across 657 SKUs and the top 10 make 11% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹18.8K, led by whey ₹3.7K, earphones ₹3.4K and speakers ₹3.0K.
 * Stock movement in progress for 1st floor expansion, aisle I fully moved to 2nd floor.
-* SLP investigation ongoing, wrong adjustments identified.
-* Clear FCC bin of ₹1.16L by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Safari Textured ABS (₹6.8K), Cosmix No-Nonsense Pro Plant (₹3.9K) and boAt Nirvana Ivy Pro Head (₹3.4K) and match with last GRN qty.
-* W2W audit of aisles J and A as Adjustment is ₹18.1K.
-* Reconcile RTO ₹14.7K with LM.</t>
+* SLP investigation ongoing, wrong adjustments identified.</t>
   </si>
   <si>
     <t xml:space="preserve">SLP Investigation is ongoing</t>
@@ -884,9 +876,7 @@
 * Adjustment is a gain of ₹82.7K, which offsets part of the loss in other buckets.
 * SKU-level net is a gain of ₹99.5K, under 10% of IH loss, so the gap is not category driven and sits in Shortpick.
 * MP shortage last month: LC1 packers did putaway after store closing, associates marked shortpick during recirculation and STO picking.
-* SLP theft investigation: ₹25,000 recovery.
-* Cycle count the shortpick bins against the ₹1.92L shortpick value.
-* Reconcile PO cancel ₹1.5K with procurement and DH.</t>
+* SLP theft investigation: ₹25,000 recovery.</t>
   </si>
   <si>
     <t xml:space="preserve">Theft Investigation – Recovery 25,000
@@ -899,11 +889,7 @@
 * Theft-prone SKUs show net loss of ₹4.5K, led by dry fruits &amp; nuts ₹2.1K, cigarettes ₹966 and premium chocolates ₹749.
 * Aisles A and B hold ₹34.7K, 59% of bin-level loss.
 * Wrong putaway incidents last month with suspected theft.
-* Escalated to SLP, investigation in progress.
-* Clear FCC bin of ₹61.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Sri Lalitha HMT Rice (₹1.9K), Sunpure Rice Bran Health Oil Pouch (₹1.4K) and Coca-Cola Zero Sugar PET Cola (₹1.1K) and match with last GRN qty.
-* W2W audit of aisles A and B as Adjustment is ₹40.0K.
-* Reconcile RTO ₹1.5K with LM and STO short receipt ₹1.7K with MH and DH.</t>
+* Escalated to SLP, investigation in progress.</t>
   </si>
   <si>
     <t xml:space="preserve">Wrong putaway incidents were identified during the last month, with a suspected theft involvement. The matter has been escalated to the SLP Team, and the investigation is currently under process.</t>
@@ -914,21 +900,13 @@
 * Top loss categories: Dairy, Bread &amp; Eggs ₹10.4K (14%), Cold Drinks &amp; Juices ₹8.2K (11%), Frozen Food ₹6.7K (9%), Munchies ₹5.8K (8%), Creatine (Protein &amp; Nutrition) ₹4.0K (6%). Share is of ₹72.1K net loss across loss-making categories.
 * Loss is spread across 1315 SKUs and the top 10 make 8% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹4.7K, led by creatine ₹2.1K, condoms ₹1.2K and serums ₹604.
-* Aisles A and I hold ₹54.0K, 57% of bin-level loss.
-* Clear FCC bin of ₹66.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount SuperYou Pro Fermented Yeast (₹1.9K), Sundrop Heart Reduce Cholesterol (₹1.8K) and Mamypoko Extra Absorb Pant Style (₹1.8K) and match with last GRN qty.
-* W2W audit of aisles A and E as Adjustment is ₹22.3K.
-* Reconcile RTO ₹763 with LM and STO short receipt ₹4.5K with MH and DH.</t>
+* Aisles A and I hold ₹54.0K, 57% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹83.2K, mainly from Adjustment ₹71.6K and FCC bin ₹9.2K.
 * Top loss categories: Rice &amp; More (Atta, Rice, Oil &amp; Dals) ₹15.2K (17%), Cleaning Essentials ₹11.1K (13%), Cups (Ice Creams &amp; More) ₹8.6K (10%), Dairy, Bread &amp; Eggs ₹7.6K (9%), Home Needs ₹7.3K (8%). Share is of ₹88.3K net loss across loss-making categories.
 * Loss is spread across 1035 SKUs and the top 10 make 13% of SKU-level loss.
-* Theft-prone SKUs show net loss of ₹7.6K, led by dry fruits &amp; nuts ₹3.2K, cigarettes ₹1.7K and premium chocolates ₹862.
-* Clear FCC bin of ₹9.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Royal Bullet Sona Masuri Steamed (₹8.9K), Daily Good Sona Masoori Boiled Rice (₹1.6K) and Surf Excel Matic Front Load (₹1.4K) and match with last GRN qty.
-* W2W audit of aisles E and B as Adjustment is ₹71.6K.
-* Reconcile STO short receipt ₹2.0K with MH and DH.</t>
+* Theft-prone SKUs show net loss of ₹7.6K, led by dry fruits &amp; nuts ₹3.2K, cigarettes ₹1.7K and premium chocolates ₹862.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹67.8K, mainly from FCC bin ₹43.0K and Adjustment ₹15.9K.
@@ -936,13 +914,7 @@
 * Top loss categories: Ice Creams &amp; More ₹19.4K (27%), Cold Drinks &amp; Juices ₹10.8K (15%), Dry Fruits &amp; Nuts (Masala, Dry Fruits &amp; More) ₹9.9K (14%), Chips &amp; Crisps (Munchies) ₹6.5K (9%), Detergent Powder &amp; Bars (Cleaning Essentials) ₹5.8K (8%). Share is of ₹71.0K net loss across loss-making categories.
 * Loss is spread across 1299 SKUs and the top 10 make 11% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹10.7K, led by dry fruits &amp; nuts ₹7.5K, cigarettes ₹1.7K and creatine ₹567.
-* Aisles H and B hold ₹27.6K, 58% of bin-level loss.
-* Clear FCC bin of ₹43.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.6K shortpick value.
-* Recount Wonderland Foods Australian Almonds (₹4.3K), Tide Plus Jasmine &amp; Rose Detergent (₹3.7K) and Oneplus Nord Buds 3 Pro in Ear TWS (₹2.3K) and match with last GRN qty.
-* W2W audit of aisles B and A as Adjustment is ₹15.9K.
-* Reconcile RTO ₹3.9K with LM and STO short receipt ₹680 with MH and DH.
-* Close out Other bins stock of ₹1.7K and post it back to inventory.</t>
+* Aisles H and B hold ₹27.6K, 58% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹58.9K, mainly from FCC bin ₹38.9K and Adjustment ₹19.5K.
@@ -952,11 +924,7 @@
 * Theft-prone SKUs show net loss of ₹3.2K, led by earphones ₹1.2K, creatine ₹1.0K and dry fruits &amp; nuts ₹418.
 * MP delta of 7.
 * Only 50% of store audited last month.
-* SSM confirms stock available in store.
-* Clear FCC bin of ₹38.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Royal Canin Labrador Retriever (₹4.2K), Daawat Sona Masuri Raw (₹3.0K) and TrueBasics Clean Plant Protein (₹2.4K) and match with last GRN qty.
-* W2W audit of aisles I and G as Adjustment is ₹19.5K.
-* Reconcile RTO ₹530 with LM.</t>
+* SSM confirms stock available in store.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹57.8K, mainly from Adjustment ₹41.4K and FCC bin ₹12.8K.
@@ -964,45 +932,26 @@
 * Loss is spread across 790 SKUs and the top 10 make 8% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹4.5K, led by cigarettes ₹1.6K, dry fruits &amp; nuts ₹1.3K and pen drives ₹1.1K.
 * Aisles K and B hold ₹30.1K, 51% of bin-level loss.
-* DHM adherence gap, SBC completion pending.
-* Clear FCC bin of ₹12.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.4K shortpick value.
-* Recount HP 64GB MicroSD Memory Card SDXC (₹1.1K), Baby Sebamed Shampoo pH 5.5 Ideal (₹829) and Fabelle Open Secret Dark Chocolate (₹819) and match with last GRN qty.
-* W2W audit of aisles B and A as Adjustment is ₹41.4K.
-* Reconcile RTO ₹948 with LM.</t>
+* DHM adherence gap, SBC completion pending.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹54.1K, mainly from FCC bin ₹29.8K, PO cancel ₹13.3K and Adjustment ₹5.8K.
 * Top loss categories: Dairy, Bread &amp; Eggs ₹12.0K (22%), Fruits &amp; Vegetables ₹7.4K (14%), Ice Creams &amp; More ₹6.0K (11%), Medical Devices (Pharma &amp; Wellness) ₹4.1K (8%), Baking Mixes &amp; Ingredients (Packaged Food) ₹3.3K (6%). Share is of ₹53.4K net loss across loss-making categories.
 * Loss is spread across 681 SKUs and the top 10 make 16% of SKU-level loss.
-* Aisles L and A hold ₹22.5K, 54% of bin-level loss.
-* Clear FCC bin of ₹29.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.4K shortpick value.
-* Recount Dr Trust USA ICheck Pro 116 (₹2.9K), Minimalist B12 Repair Complex Face (₹1.8K) and Morde Dark Compound Suitable (₹1.5K) and match with last GRN qty.
-* W2W audit of aisles A and H as Adjustment is ₹5.8K.
-* Reconcile RTO ₹3.8K with LM and PO cancel ₹13.3K with procurement and DH.</t>
+* Aisles L and A hold ₹22.5K, 54% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹54.1K, mainly from FCC bin ₹23.7K, Adjustment ₹20.5K and Shortpick ₹7.7K.
 * Top loss categories: Whey Protein (Protein &amp; Nutrition) ₹7.0K (15%), Kitchen Appliances (Electronics &amp; Appliances) ₹6.4K (14%), Cold Drinks &amp; Juices ₹5.2K (11%), Rice &amp; More (Atta, Rice, Oil &amp; Dals) ₹3.9K (9%), Frozen Food ₹3.8K (8%). Share is of ₹45.6K net loss across loss-making categories.
 * Loss is spread across 546 SKUs and the top 10 make 27% of SKU-level loss.
-* Theft-prone SKUs show net loss of ₹9.6K, led by whey ₹7.6K, premium chocolates ₹1.6K and cigarettes ₹475.
-* Clear FCC bin of ₹23.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹7.7K shortpick value.
-* Recount Only What's Needed 24g Whey (₹4.2K), Philips Air Fryer NA120/00, 1500W (₹3.7K) and MuscleBlaze Raw Whey Protein (₹3.4K) and match with last GRN qty.
-* W2W audit of aisles C and I as Adjustment is ₹20.5K.
-* Reconcile RTO ₹584 with LM and STO short receipt ₹1.6K with MH and DH.</t>
+* Theft-prone SKUs show net loss of ₹9.6K, led by whey ₹7.6K, premium chocolates ₹1.6K and cigarettes ₹475.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹52.2K, mainly from Adjustment ₹37.0K and FCC bin ₹13.7K.
 * Top loss categories: Ice Creams &amp; More ₹7.8K (15%), Cigarettes (Paan Corner) ₹6.3K (12%), Dairy, Bread &amp; Eggs ₹6.0K (12%), Frozen Food ₹5.8K (11%), Rice &amp; More (Atta, Rice, Oil &amp; Dals) ₹5.1K (10%). Share is of ₹52.1K net loss across loss-making categories.
 * Loss is spread across 696 SKUs and the top 10 make 16% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹8.0K, led by cigarettes ₹6.1K, creatine ₹1.1K and dry fruits &amp; nuts ₹787.
-* Aisles D and O hold ₹30.1K, 53% of bin-level loss.
-* Clear FCC bin of ₹13.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Bigmuscles Nutrition Premium Gold (₹2.9K), Marlboro Gold Advance Cigarettes (₹2.3K) and Players Minty Cool Fresh Taste (₹2.0K) and match with last GRN qty.
-* W2W audit of aisles D and C as Adjustment is ₹37.0K.
-* Reconcile STO short receipt ₹1.4K with MH and DH.</t>
+* Aisles D and O hold ₹30.1K, 53% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹51.8K, mainly from FCC bin ₹27.6K, Adjustment ₹16.8K and Shortpick ₹5.8K.
@@ -1011,35 +960,21 @@
 * Theft-prone SKUs show net loss of ₹6.9K, led by cigarettes ₹3.3K, premium chocolates ₹1.9K and whey ₹1.2K.
 * Aisles I and H hold ₹32.8K, 67% of bin-level loss.
 * CCA delta of 3, SBC not done.
-* Wrong putaway led to stock spread across bins and high FC.
-* Clear FCC bin of ₹27.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹5.8K shortpick value.
-* Recount Classic Ice Burst Fresh Mint (₹2.9K), Logitech Pebble Keys 2 (₹2.6K) and Superior MP Wheat Atta, 0% Maida (₹2.0K) and match with last GRN qty.
-* W2W audit of aisles H and N as Adjustment is ₹16.8K.
-* Reconcile RTO ₹1.6K with LM.</t>
+* Wrong putaway led to stock spread across bins and high FC.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹49.5K, mainly from Adjustment ₹34.2K and FCC bin ₹13.5K.
 * Top loss categories: Chocolates (Sweet Cravings) ₹10.9K (25%), Ice Creams &amp; More ₹8.3K (19%), Atta, Rice, Oil &amp; Dals ₹6.7K (15%), Chips &amp; Crisps (Munchies) ₹4.0K (9%), Fruits &amp; Vegetables ₹2.9K (7%). Share is of ₹43.6K net loss across loss-making categories.
 * Loss is spread across 808 SKUs and the top 10 make 15% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹7.2K, led by premium chocolates ₹4.4K, dry fruits &amp; nuts ₹1.6K and earphones ₹1.0K.
-* Aisles J and K hold ₹17.0K, 59% of bin-level loss.
-* Clear FCC bin of ₹13.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Royal Bullet Sona Masuri Steamed (₹1.8K), Gala No Dust Floor Cleaning Broom (₹1.5K) and Mr. Gold Groundnut Oil Pouch (₹929) and match with last GRN qty.
-* W2W audit of aisles J and D as Adjustment is ₹34.2K.
-* Reconcile RTO ₹541 with LM.
-* Close out Other bins stock of ₹1.3K and post it back to inventory.</t>
+* Aisles J and K hold ₹17.0K, 59% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹48.9K, mainly from Adjustment ₹31.1K and FCC bin ₹16.9K.
 * Top loss categories: Ice Creams &amp; More ₹21.3K (30%), Frozen Food ₹20.2K (29%), Dairy, Bread &amp; Eggs ₹9.8K (14%), Fresh Vegetables (Fruits &amp; Vegetables) ₹7.0K (10%), Chicken (Meats, Fish &amp; Eggs) ₹2.6K (4%). Share is of ₹70.4K net loss across loss-making categories.
 * Loss is spread across 1028 SKUs and the top 10 make 11% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹2.4K, led by cigarettes ₹1.7K and premium chocolates ₹769.
-* Aisles M and L hold ₹56.3K, 90% of bin-level loss.
-* Clear FCC bin of ₹16.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount GTS Original Kolam Rice (₹2.6K), Freedom Refined Sunflower Oil (₹1.8K) and Jivo Pomace Olive Oil (₹891) and match with last GRN qty.
-* W2W audit of aisles K and Q as Adjustment is ₹31.1K.
-* Reconcile RTO ₹595 with LM.</t>
+* Aisles M and L hold ₹56.3K, 90% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">Narasimhamurthy R</t>
@@ -1055,11 +990,7 @@
 * Aisles A and G hold ₹40.3K, 77% of bin-level loss.
 * Peak CCA unable to add excess stock.
 * DH CCA deployed for SBC.
-* Wrong putaway reported.
-* Clear FCC bin of ₹20.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.4K shortpick value.
-* Recount Sandisk microSDXC UHS-I Memory (₹1.8K), Jivo Sunflower Cold Pressed Oil (₹1.7K) and Daily Good Sona Masoori Boiled Rice (₹1.6K) and match with last GRN qty.
-* W2W audit of aisles A and G as Adjustment is ₹26.8K.</t>
+* Wrong putaway reported.</t>
   </si>
   <si>
     <t xml:space="preserve">40K </t>
@@ -1078,10 +1009,7 @@
 * Top loss categories: Atta, Rice, Oil &amp; Dals ₹5.0K (15%), Chips &amp; Crisps (Munchies) ₹3.7K (11%), Tea, Coffee &amp; More ₹3.7K (11%), Paneer &amp; Cream (Dairy, Bread &amp; Eggs) ₹2.7K (8%), Fruits &amp; Vegetables ₹2.7K (8%). Share is of ₹32.7K net loss across loss-making categories.
 * Loss is spread across 809 SKUs and the top 10 make 11% of SKU-level loss.
 * FOCO to COCO conversion.
-* W2W done at handover.
-* Clear FCC bin of ₹4.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Amazon Pay Shagun Gift Card - INR (₹2.0K), Evereve Overnight Disposable (₹1.3K) and Nescafe Gold Blend Rich And Smooth (₹1.1K) and match with last GRN qty.
-* W2W audit of aisles C and B as Adjustment is ₹44.0K.</t>
+* W2W done at handover.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Malleshpalya Shrinkage - 2026-10-05</t>
@@ -1093,11 +1021,7 @@
     <t xml:space="preserve">* Total IH loss is ₹47.2K, mainly from FCC bin ₹17.5K, Adjustment ₹15.2K and STO short receipt ₹12.1K.
 * SKU-level net is ₹2.0K, under 10% of IH loss, so the gap is not category driven and sits in FCC bin.
 * Theft-prone SKUs show net loss of ₹3.3K, led by dry fruits &amp; nuts ₹2.0K, perfumes ₹983 and cigarettes ₹359.
-* Aisles E and K hold ₹18.8K, 58% of bin-level loss.
-* Clear FCC bin of ₹17.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Jivo Pomace Olive Oil (₹6.3K), Ariel Matic Detergent Powder Front (₹980) and Keshar Kali Wada Kolam Rice (₹835) and match with last GRN qty.
-* W2W audit of aisles E and C as Adjustment is ₹15.2K.
-* Reconcile RTO ₹1.7K with LM and STO short receipt ₹12.1K with MH and DH.</t>
+* Aisles E and K hold ₹18.8K, 58% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹47.1K, mainly from FCC bin ₹27.2K, Adjustment ₹9.4K and RTO loss ₹6.7K.
@@ -1105,11 +1029,7 @@
 * Theft-prone SKUs show net loss of ₹3.6K, led by dry fruits &amp; nuts ₹1.8K, perfumes ₹1.1K and premium chocolates ₹447.
 * DHM and SI monitoring gap.
 * Packers marked FC with stock available in primary bin.
-* SS RTO not cleared on time.
-* Clear FCC bin of ₹27.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Gold Winner Refined Sunflower Oil (₹3.4K), Classic Ice Burst Fresh Mint (₹1.9K) and Aptamil Gold 2 Follow up Infant (₹1.6K) and match with last GRN qty.
-* W2W audit of aisles X and M as Adjustment is ₹9.4K.
-* Reconcile RTO ₹6.7K with LM and STO short receipt ₹3.5K with MH and DH.</t>
+* SS RTO not cleared on time.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kudlu</t>
@@ -1121,12 +1041,7 @@
     <t xml:space="preserve">* Total IH loss is ₹46.4K, mainly from Adjustment ₹27.6K and FCC bin ₹14.1K.
 * Top loss categories: Sticks (Ice Creams &amp; More) ₹11.4K (32%), Chips &amp; Crisps (Munchies) ₹4.5K (12%), Rice &amp; More (Atta, Rice, Oil &amp; Dals) ₹4.0K (11%), Cold Drinks &amp; Juices ₹3.3K (9%), Home Needs ₹2.2K (6%). Share is of ₹36.1K net loss across loss-making categories.
 * Loss is spread across 1043 SKUs and the top 10 make 6% of SKU-level loss.
-* Aisles C and I hold ₹22.8K, 67% of bin-level loss.
-* Clear FCC bin of ₹14.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹3.9K shortpick value.
-* Recount GTS Original Kolam Rice (₹862), Liquid I.V. Hydration Multiplier (₹785) and Daawat Sona Masuri Rice Medium (₹666) and match with last GRN qty.
-* W2W audit of aisles C and D as Adjustment is ₹27.6K.
-* Reconcile RTO ₹804 with LM.</t>
+* Aisles C and I hold ₹22.8K, 67% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bommanahalli</t>
@@ -1136,9 +1051,7 @@
 * Majority impact is from STO short receipt of ₹41.4K. Excluding this, the store is ₹2.4K in loss.
 * SKU-level net is a gain of ₹4.5K, under 10% of IH loss, so the gap is not category driven and sits in STO short receipt.
 * Aisles B and S hold ₹4.8K, 66% of bin-level loss.
-* STO from Mathikere not dispatched as per SOP, STO putaway is the main bucket.
-* Clear FCC bin of ₹2.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile STO short receipt ₹41.4K with MH and DH.</t>
+* STO from Mathikere not dispatched as per SOP, STO putaway is the main bucket.</t>
   </si>
   <si>
     <t xml:space="preserve">Balaji G</t>
@@ -1151,13 +1064,7 @@
 * Theft-prone SKUs show net loss of ₹3.2K, led by whey ₹2.8K and earphones ₹415.
 * Aisles I and J hold ₹30.9K, 74% of bin-level loss.
 * Wrong putaway in frozen, SKUs stacked in deep bins.
-* Blind spots in milk room, munching of chocolates, ice cream and chips identified.
-* Clear FCC bin of ₹31.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹4.0K shortpick value.
-* Recount Avvatar Performance Whey Protein (₹2.8K), Royal Bullet Sona Masuri Steamed (₹1.8K) and Desi Farms Cow Ghee (₹1.6K) and match with last GRN qty.
-* W2W audit of aisles B and K as Adjustment is ₹3.2K.
-* Reconcile RTO ₹1.7K with LM.
-* Close out Other bins stock of ₹2.9K and post it back to inventory.</t>
+* Blind spots in milk room, munching of chocolates, ice cream and chips identified.</t>
   </si>
   <si>
     <t xml:space="preserve">Ashwath S</t>
@@ -1166,10 +1073,7 @@
     <t xml:space="preserve">* Total IH loss is ₹43.0K, mainly from Adjustment ₹33.6K and FCC bin ₹9.1K.
 * Top loss categories: Atta, Rice, Oil &amp; Dals ₹8.8K (25%), Ice Creams &amp; More ₹4.9K (14%), Veg Snacks (Frozen Food) ₹4.9K (14%), Chips &amp; Crisps (Munchies) ₹3.5K (10%), Masala, Dry Fruits &amp; More ₹2.9K (8%). Share is of ₹36.0K net loss across loss-making categories.
 * Loss is spread across 624 SKUs and the top 10 make 13% of SKU-level loss.
-* Aisles C and H hold ₹29.8K, 75% of bin-level loss.
-* Clear FCC bin of ₹9.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Pampers Active Baby Taped Style (₹1.5K), Daily Good Sona Masoori Steam Rice (₹1.4K) and Figaro Extra Light Tasting Olive (₹963) and match with last GRN qty.
-* W2W audit of aisles C and B as Adjustment is ₹33.6K.</t>
+* Aisles C and H hold ₹29.8K, 75% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹43.0K, mainly from PO cancel ₹32.9K and FCC bin ₹26.1K.
@@ -1177,32 +1081,20 @@
 * Adjustment is a gain of ₹18.6K, which offsets part of the loss in other buckets.
 * SKU-level net is ₹287, under 10% of IH loss, so the gap is not category driven and sits in PO cancel.
 * Theft-prone SKUs show net loss of ₹11.5K, led by whey ₹3.7K, chargers ₹3.0K and earphones ₹1.6K.
-* Aisles H and C hold ₹27.1K, 84% of bin-level loss.
-* Clear FCC bin of ₹26.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount MuscleBlaze Biozyme Performance (₹3.7K), Freedom Refined Sunflower Oil (₹2.6K) and GTS Original Kolam Rice (₹2.6K) and match with last GRN qty.
-* Reconcile STO short receipt ₹2.1K with MH and DH and PO cancel ₹32.9K with procurement and DH.</t>
+* Aisles H and C hold ₹27.1K, 84% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹42.8K, mainly from Adjustment ₹23.7K, FCC bin ₹12.6K and Shortpick ₹5.7K.
 * SKU-level net is a gain of ₹138, under 10% of IH loss, so the gap is not category driven and sits in FCC bin.
 * Theft-prone SKUs show net loss of ₹8.8K, led by whey ₹8.7K, cigars ₹71 and perfumes ₹64.
-* Aisles C and H hold ₹36.0K, 63% of bin-level loss.
-* Clear FCC bin of ₹12.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹5.7K shortpick value.
-* Recount TrueBasics Clean Whey Protein (₹8.7K), Pampers Active Baby Taped Style (₹1.4K) and Cadbury Bournville Rich Cocoa 70% (₹1.1K) and match with last GRN qty.
-* W2W audit of aisle C as Adjustment is ₹23.7K.
-* Reconcile RTO ₹746 with LM.</t>
+* Aisles C and H hold ₹36.0K, 63% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹42.8K, mainly from Adjustment ₹29.7K and FCC bin ₹9.3K.
 * Top loss categories: Atta, Rice, Oil &amp; Dals ₹7.2K (16%), Fresh Vegetables (Fruits &amp; Vegetables) ₹6.3K (14%), Muesli &amp; Oats (Breakfast &amp; Sauces) ₹5.4K (12%), Munchies ₹4.3K (10%), Cold Drinks &amp; Juices ₹4.1K (9%). Share is of ₹44.0K net loss across loss-making categories.
 * Loss is spread across 567 SKUs and the top 10 make 15% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹5.1K, led by dry fruits &amp; nuts ₹3.4K, whey ₹1.2K and pre-workout ₹386.
-* Aisles A and B hold ₹30.1K, 72% of bin-level loss.
-* Clear FCC bin of ₹9.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹3.5K shortpick value.
-* Recount Nutraj Cashew Nuts Kaju (₹1.6K), NAKPRO Impact Whey Protein blend (₹1.2K) and Surf Excel Matic Front Load (₹1.1K) and match with last GRN qty.
-* W2W audit of aisles A and B as Adjustment is ₹29.7K.</t>
+* Aisles A and B hold ₹30.1K, 72% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">Suhas N</t>
@@ -1218,11 +1110,7 @@
 * Aisles E and D hold ₹19.0K, 57% of bin-level loss.
 * Mass theft involvement identified.
 * SLP investigation completed, IR pending.
-* Salary hold and stock adjustment raised, SLP recovery ₹48,000 (18K + 30K).
-* Clear FCC bin of ₹9.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Nandini Pure Ghee Pouch (₹22.5K), Tata Sampann Unpolished Toor (₹2.8K) and Popular Essentials Premium Jeera (₹2.4K) and match with last GRN qty.
-* W2W audit of aisles E and D as Adjustment is ₹29.2K.
-* Reconcile RTO ₹3.0K with LM.</t>
+* Salary hold and stock adjustment raised, SLP recovery ₹48,000 (18K + 30K).</t>
   </si>
   <si>
     <t xml:space="preserve">Salary Hold Request – Theft Investigation and Recovery // BLR-Thyagaraja Nagar //  &amp;  Stock Adjustment Request – Theft Case // BLR-Thyagaraja Nagar /</t>
@@ -1237,11 +1125,7 @@
     <t xml:space="preserve">* Total IH loss is ₹41.5K, mainly from FCC bin ₹24.0K and Adjustment ₹16.7K.
 * Top loss categories: Atta, Rice, Oil &amp; Dals ₹6.2K (16%), Namkeens (Munchies) ₹4.7K (12%), Sweet Cravings ₹4.3K (11%), Cups (Ice Creams &amp; More) ₹3.7K (9%), Fruits &amp; Vegetables ₹3.3K (8%). Share is of ₹39.3K net loss across loss-making categories.
 * Loss is spread across 811 SKUs and the top 10 make 13% of SKU-level loss.
-* CCA delta, 3 CCAs now hired.
-* Clear FCC bin of ₹24.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Nandini Pure Ghee Pouch (₹1.8K), Mr.Gold Refined Rice Bran Oil Pouch (₹1.6K) and Wellwith Sea Buckthorn Pulp (₹1.2K) and match with last GRN qty.
-* W2W audit of aisles D and C as Adjustment is ₹16.7K.
-* Reconcile RTO ₹843 with LM.</t>
+* CCA delta, 3 CCAs now hired.</t>
   </si>
   <si>
     <t xml:space="preserve">Complete losses will be recovered (40k)</t>
@@ -1251,12 +1135,7 @@
 * Top loss categories: Whey Protein (Protein &amp; Nutrition) ₹9.5K (21%), Earphones &amp; Headphones (Electronics &amp; Appliances) ₹7.9K (17%), Sweet Cravings ₹4.4K (10%), Munchies ₹4.3K (9%), Cigarettes (Paan Corner) ₹3.6K (8%). Share is of ₹45.9K net loss across loss-making categories.
 * Loss is spread across 807 SKUs and the top 10 make 19% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹23.2K, led by whey ₹9.5K, earphones ₹5.2K and cigarettes ₹3.9K.
-* Aisles E and F hold ₹28.4K, 72% of bin-level loss.
-* Clear FCC bin of ₹6.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹3.9K shortpick value.
-* Recount TrueBasics Clean Whey Protein (₹8.7K), Apple Earpods wired Earphone (₹4.0K) and Marlboro Red (₹2.6K) and match with last GRN qty.
-* W2W audit of aisles E and F as Adjustment is ₹27.9K.
-* Reconcile RTO ₹2.3K with LM.</t>
+* Aisles E and F hold ₹28.4K, 72% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kogilu Road</t>
@@ -1266,23 +1145,14 @@
 * Top loss categories: Ice Creams &amp; More ₹12.5K (28%), Frozen Food ₹9.8K (22%), Dairy, Bread &amp; Eggs ₹4.5K (10%), Chips &amp; Crisps (Munchies) ₹3.7K (8%), Dry Fruits &amp; Nuts (Masala, Dry Fruits &amp; More) ₹1.6K (4%). Share is of ₹44.2K net loss across loss-making categories.
 * Loss is spread across 604 SKUs and the top 10 make 12% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹2.1K, led by dry fruits &amp; nuts ₹1.1K, cigarettes ₹855 and chargers ₹111.
-* Aisles K and E hold ₹35.6K, 81% of bin-level loss.
-* Clear FCC bin of ₹6.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹4.0K shortpick value.
-* Recount Daily Good Sona Masoori Boiled Rice (₹1.6K), Nestle Nan Excellapro Stage 3 (₹1.6K) and Wellcore Micronised Tropical Tango (₹1.0K) and match with last GRN qty.
-* W2W audit of aisles E and A as Adjustment is ₹30.2K.
-* Reconcile RTO ₹810 with LM.</t>
+* Aisles K and E hold ₹35.6K, 81% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹40.2K, mainly from Adjustment ₹29.1K and FCC bin ₹9.7K.
 * Top loss categories: Fruits &amp; Vegetables ₹16.6K (34%), Milk (Dairy, Bread &amp; Eggs) ₹10.4K (22%), Cold Drinks &amp; Juices ₹5.5K (11%), Whey Protein (Protein &amp; Nutrition) ₹3.8K (8%), Cones (Ice Creams &amp; More) ₹2.6K (5%). Share is of ₹48.3K net loss across loss-making categories.
 * Loss is spread across 941 SKUs and the top 10 make 13% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹6.8K, led by whey ₹4.3K, premium chocolates ₹1.2K and cigarettes ₹984.
-* FnV adjustments done by QA without DHM knowledge, 2 QA associates removed.
-* Clear FCC bin of ₹9.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount TrueBasics Clean Whey Protein (₹4.3K), Bisleri Packaged Drinking Water (₹1.7K) and Daily Good Sona Masoori Boiled Rice (₹1.6K) and match with last GRN qty.
-* W2W audit of aisles H and I as Adjustment is ₹29.1K.
-* Reconcile RTO ₹773 with LM.</t>
+* FnV adjustments done by QA without DHM knowledge, 2 QA associates removed.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-CV RAMAN NAGAR NEW</t>
@@ -1292,21 +1162,13 @@
 * Top loss categories: Fruits &amp; Vegetables ₹15.0K (41%), Batters &amp; Mixes (Dairy, Bread &amp; Eggs) ₹4.8K (13%), Atta (Atta, Rice, Oil &amp; Dals) ₹3.9K (11%), Chocolates (Sweet Cravings) ₹2.2K (6%), Cold Drinks &amp; Juices ₹1.6K (4%). Share is of ₹36.2K net loss across loss-making categories.
 * Loss is spread across 531 SKUs and the top 10 make 22% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹5.7K, led by gift cards ₹3.3K, dry fruits &amp; nuts ₹1.3K and creatine ₹520.
-* Aisles G and H hold ₹19.9K, 55% of bin-level loss.
-* Clear FCC bin of ₹11.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Amazon Pay Shagun Gift Card - INR (₹4.9K), Superior MP Wheat Atta, 0% Maida (₹2.5K) and Nandini Pure Ghee Pouch (₹1.2K) and match with last GRN qty.
-* W2W audit of aisles G and D as Adjustment is ₹14.0K.
-* Reconcile RTO ₹1.4K with LM, STO short receipt ₹2.0K with MH and DH and PO cancel ₹9.9K with procurement and DH.</t>
+* Aisles G and H hold ₹19.9K, 55% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹39.9K, mainly from Adjustment ₹19.6K and FCC bin ₹18.3K.
 * Top loss categories: Ice Creams &amp; More ₹8.1K (19%), Chocolates (Sweet Cravings) ₹6.8K (16%), Cold Drinks &amp; Juices ₹6.0K (14%), Cheese (Dairy, Bread &amp; Eggs) ₹4.8K (12%), Energy Bars (Munchies) ₹2.2K (5%). Share is of ₹41.9K net loss across loss-making categories.
 * Loss is spread across 743 SKUs and the top 10 make 11% of SKU-level loss.
-* Aisles M and L hold ₹21.5K, 54% of bin-level loss.
-* Clear FCC bin of ₹18.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Zippo Simple Spade Design Classic (₹2.2K), Lamp Oil Pet Bottle Dheepam (₹1.6K) and Sunpure Filtered Groundnut Oil (₹1.2K) and match with last GRN qty.
-* W2W audit of aisles L and K as Adjustment is ₹19.6K.
-* Reconcile RTO ₹1.6K with LM.</t>
+* Aisles M and L hold ₹21.5K, 54% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹39.7K, mainly from Adjustment ₹28.8K and FCC bin ₹10.9K.
@@ -1314,10 +1176,7 @@
 * Loss is spread across 723 SKUs and the top 10 make 16% of SKU-level loss.
 * Aisles G and O hold ₹25.3K, 63% of bin-level loss.
 * 3 MP gap.
-* SBC pending on part of bins.
-* Clear FCC bin of ₹10.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount GTS Original Kolam Rice (₹5.1K), Daily Good Sona Masoori Raw Rice (₹1.8K) and Daily Good Sona Masoori Steam Rice (₹1.4K) and match with last GRN qty.
-* W2W audit of aisles G and K as Adjustment is ₹28.8K.</t>
+* SBC pending on part of bins.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-HSR-2</t>
@@ -1327,11 +1186,7 @@
 * Top loss categories: Ice Creams &amp; More ₹14.4K (40%), Munchies ₹6.3K (17%), Cheese (Dairy, Bread &amp; Eggs) ₹4.5K (13%), Dry Fruits &amp; Nuts (Masala, Dry Fruits &amp; More) ₹2.5K (7%), Cold Drinks &amp; Juices ₹2.1K (6%). Share is of ₹36.2K net loss across loss-making categories.
 * Loss is spread across 618 SKUs and the top 10 make 15% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹3.7K, led by dry fruits &amp; nuts ₹3.3K and premium chocolates ₹389.
-* Aisles L and H hold ₹23.0K, 66% of bin-level loss.
-* Clear FCC bin of ₹12.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹5.4K shortpick value.
-* Recount GTS Original Kolam Rice (₹2.6K), Pampers All Round Protection Pant (₹1.9K) and Nutraj Phool Makhana Popped (₹1.1K) and match with last GRN qty.
-* W2W audit of aisles H and F as Adjustment is ₹22.0K.</t>
+* Aisles L and H hold ₹23.0K, 66% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kothnur New</t>
@@ -1340,12 +1195,7 @@
     <t xml:space="preserve">* Total IH loss is ₹39.4K, mainly from FCC bin ₹18.4K and Adjustment ₹16.4K.
 * SKU-level net is a gain of ₹7.2K, under 10% of IH loss, so the gap is not category driven and sits in FCC bin.
 * Aisles A and J hold ₹8.9K, 82% of bin-level loss.
-* ATA mode conversion switched off CC, add back access not available.
-* Clear FCC bin of ₹18.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.8K shortpick value.
-* Recount GTS Original Kolam Rice (₹2.6K), Shree Akshara Sona Masoori Steam (₹1.6K) and Brooke Bond Red Label Tea (₹1.5K) and match with last GRN qty.
-* W2W audit of aisles A and G as Adjustment is ₹16.4K.
-* Reconcile RTO ₹751 with LM and STO short receipt ₹756 with MH and DH.</t>
+* ATA mode conversion switched off CC, add back access not available.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹38.3K, mainly from Adjustment ₹23.5K and FCC bin ₹11.4K.
@@ -1353,11 +1203,7 @@
 * Loss is spread across 454 SKUs and the top 10 make 15% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹6.6K, led by whey ₹4.5K, perfumes ₹1.2K and chargers ₹889.
 * Putaway issue due to aisle congestion.
-* Aisles 1 and M affected.
-* Clear FCC bin of ₹11.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount TrueBasics Clean Whey Protein (₹4.5K), Pampers Premium Care Pants M (₹2.7K) and Yonex Astrox Attack 9 Badminton (₹2.6K) and match with last GRN qty.
-* W2W audit of aisles U and W as Adjustment is ₹23.5K.
-* Reconcile RTO ₹3.5K with LM.</t>
+* Aisles 1 and M affected.</t>
   </si>
   <si>
     <t xml:space="preserve">Mohaideen DH</t>
@@ -1368,10 +1214,7 @@
 * Top loss categories: Chips &amp; Crisps (Munchies) ₹12.4K (29%), Oil (Atta, Rice, Oil &amp; Dals) ₹6.0K (14%), Whey Protein (Protein &amp; Nutrition) ₹5.6K (13%), Biscuits ₹3.5K (8%), Fruits &amp; Vegetables ₹3.5K (8%). Share is of ₹42.5K net loss across loss-making categories.
 * Loss is spread across 929 SKUs and the top 10 make 12% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹5.8K, led by whey ₹3.7K, creatine ₹781 and pen drives ₹542.
-* Aisles A and C hold ₹33.6K, 81% of bin-level loss.
-* Clear FCC bin of ₹28.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount TrueBasics Clean Raw Whey Protein (₹3.7K), Saffola Gold Rice Bran &amp; Sunflower (₹2.2K) and Baby Sebamed Gentle Wash pH 5.5 (₹783) and match with last GRN qty.
-* W2W audit of aisles A and C as Adjustment is ₹7.4K.</t>
+* Aisles A and C hold ₹33.6K, 81% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Manjunatha layout</t>
@@ -1381,12 +1224,7 @@
 * Top loss categories: Dairy, Bread &amp; Eggs ₹19.3K (37%), Munchies ₹7.9K (15%), Sweet Cravings ₹4.7K (9%), Packaged Food ₹3.8K (7%), Cold Drinks &amp; Juices ₹3.5K (7%). Share is of ₹52.5K net loss across loss-making categories.
 * Loss is spread across 806 SKUs and the top 10 make 14% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹3.3K, led by trimmers ₹2.8K, premium chocolates ₹436 and deos ₹83.
-* Aisles B and H hold ₹19.9K, 56% of bin-level loss.
-* Clear FCC bin of ₹12.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.0K shortpick value.
-* Recount Philips MG3917/15 All-in-One (₹3.9K), Superior MP Wheat Atta, 0% Maida (₹1.4K) and Gowardhan Pure Cow Ghee Jar (₹1.4K) and match with last GRN qty.
-* W2W audit of aisles B and C as Adjustment is ₹15.3K.
-* Reconcile RTO ₹1.3K with LM and STO short receipt ₹7.0K with MH and DH.</t>
+* Aisles B and H hold ₹19.9K, 56% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BHADRAPPA LAYOUT NETWORK</t>
@@ -1396,11 +1234,7 @@
 * Majority impact is from FCC bin of ₹36.1K. Excluding this, the store is ₹1.1K positive.
 * Adjustment is a gain of ₹24.5K, which offsets part of the loss in other buckets.
 * SKU-level net is a gain of ₹19.0K, under 10% of IH loss, so the gap is not category driven and sits in FCC bin.
-* Aisles E and M hold ₹9.3K, 51% of bin-level loss.
-* Clear FCC bin of ₹36.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹5.2K shortpick value.
-* Recount GTS Original Kolam Rice (₹2.6K), Nandini Pure Ghee Pouch (₹2.4K) and Gold Winner Refined Sunflower Oil (₹1.9K) and match with last GRN qty.
-* Reconcile RTO ₹13.1K with LM and STO short receipt ₹5.0K with MH and DH.</t>
+* Aisles E and M hold ₹9.3K, 51% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-JP Nagar New</t>
@@ -1414,10 +1248,7 @@
 * Adjustment is a gain of ₹2.9K, which offsets part of the loss in other buckets.
 * Top loss categories: Chips &amp; Crisps (Munchies) ₹10.1K (27%), Chicken (Meats, Fish &amp; Eggs) ₹9.3K (25%), Dairy, Bread &amp; Eggs ₹7.3K (19%), Dry Fruits &amp; Nuts (Masala, Dry Fruits &amp; More) ₹3.1K (8%), Fruit Juices &amp; Drinks (Cold Drinks &amp; Juices) ₹1.7K (4%). Share is of ₹37.6K net loss across loss-making categories.
 * Loss is spread across 708 SKUs and the top 10 make 18% of SKU-level loss.
-* Theft-prone SKUs show net loss of ₹3.4K, led by dry fruits &amp; nuts ₹3.4K.
-* Clear FCC bin of ₹33.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.0K shortpick value.
-* Recount Nutraj Cashew Nuts Kaju (₹2.1K), Taj Mahal Tea Rich And Flavourful (₹1.3K) and Sunpure Refined Sunflower Oil (₹1.3K) and match with last GRN qty.</t>
+* Theft-prone SKUs show net loss of ₹3.4K, led by dry fruits &amp; nuts ₹3.4K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Nehru Nagar</t>
@@ -1430,11 +1261,7 @@
 * Majority impact is from FCC bin of ₹21.4K. Excluding this, the store is ₹11.9K in loss.
 * Top loss categories: Fruits &amp; Vegetables ₹4.6K (20%), Dairy, Bread &amp; Eggs ₹4.4K (20%), Rice &amp; More (Atta, Rice, Oil &amp; Dals) ₹3.1K (14%), Ice Creams &amp; More ₹1.9K (9%), Baby Diapering (Baby Care) ₹1.8K (8%). Share is of ₹22.5K net loss across loss-making categories.
 * Loss is spread across 560 SKUs and the top 10 make 16% of SKU-level loss.
-* Aisles I and K hold ₹8.5K, 57% of bin-level loss.
-* Clear FCC bin of ₹21.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Daily Good Sona Masoori Raw Rice (₹1.8K), Pampers Premium Care Pants L 44 No (₹1.2K) and Bisleri Packaged Drinking Water (₹1.1K) and match with last GRN qty.
-* W2W audit of aisles K and E as Adjustment is ₹7.6K.
-* Reconcile RTO ₹4.0K with LM.</t>
+* Aisles I and K hold ₹8.5K, 57% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BELLANDUR-4</t>
@@ -1443,11 +1270,7 @@
     <t xml:space="preserve">* Total IH loss is ₹32.6K, mainly from Adjustment ₹21.3K and FCC bin ₹9.5K.
 * Top loss categories: Dairy, Bread &amp; Eggs ₹6.7K (34%), Atta, Rice, Oil &amp; Dals ₹3.2K (16%), Fruit Juices &amp; Drinks (Cold Drinks &amp; Juices) ₹2.0K (10%), Biscuits ₹1.9K (10%), Munchies ₹1.7K (9%). Share is of ₹19.6K net loss across loss-making categories.
 * Loss is spread across 450 SKUs and the top 10 make 18% of SKU-level loss.
-* Aisles A and H hold ₹16.1K, 70% of bin-level loss.
-* Clear FCC bin of ₹9.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Superior MP Wheat Atta, 0% Maida (₹857), Tata Sampann Unpolished Kabuli (₹853) and RAW Pressery Coconut Water No (₹802) and match with last GRN qty.
-* W2W audit of aisles A and F as Adjustment is ₹21.3K.
-* Reconcile STO short receipt ₹1.4K with MH and DH.</t>
+* Aisles A and H hold ₹16.1K, 70% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kamakshipalya</t>
@@ -1457,10 +1280,7 @@
 * Top loss categories: Ice Creams &amp; More ₹12.9K (29%), Veg Snacks (Frozen Food) ₹4.9K (11%), Curd &amp; Probiotic Drink (Dairy, Bread &amp; Eggs) ₹4.0K (9%), Masala, Dry Fruits &amp; More ₹3.0K (7%), Home Needs ₹2.8K (6%). Share is of ₹44.1K net loss across loss-making categories.
 * Loss is spread across 866 SKUs and the top 10 make 10% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹2.3K, led by earphones ₹1.2K, cigarettes ₹480 and serums ₹304.
-* Aisles Q and G hold ₹23.5K, 55% of bin-level loss.
-* Clear FCC bin of ₹7.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Superior MP Wheat Atta, 0% Maida (₹1.4K), Apple Earpods wired Earphone (₹1.3K) and Nandini Pure Ghee Pouch (₹1.2K) and match with last GRN qty.
-* W2W audit of aisles G and D as Adjustment is ₹24.8K.</t>
+* Aisles Q and G hold ₹23.5K, 55% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RAMAMURTHY NAGAR NEW</t>
@@ -1470,12 +1290,7 @@
 * Top loss categories: Atta, Rice, Oil &amp; Dals ₹9.9K (28%), Frozen Food ₹5.0K (14%), Ice Creams &amp; More ₹4.7K (13%), Cold Drinks &amp; Juices ₹4.6K (13%), Cleaning Essentials ₹2.7K (8%). Share is of ₹35.2K net loss across loss-making categories.
 * Loss is spread across 602 SKUs and the top 10 make 13% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹2.0K, led by premium chocolates ₹2.0K.
-* Aisles I and F hold ₹22.1K, 75% of bin-level loss.
-* Clear FCC bin of ₹9.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹6.6K shortpick value.
-* Recount Whiskas Adult Ocean Fish Flavour (₹1.5K), Chokola Cosmos Chocolate Hamper (₹1.4K) and Gulab Groundnut (Peanut) Cold (₹1.3K) and match with last GRN qty.
-* W2W audit of aisles F and B as Adjustment is ₹14.3K.
-* Reconcile RTO ₹776 with LM.</t>
+* Aisles I and F hold ₹22.1K, 75% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹30.4K, mainly from Adjustment ₹19.0K and FCC bin ₹10.9K.
@@ -1483,10 +1298,7 @@
 * Loss is spread across 720 SKUs and the top 10 make 15% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹3.7K, led by cigarettes ₹3.2K, perfumes ₹272 and deos ₹262.
 * Aisles D and J hold ₹24.7K, 71% of bin-level loss.
-* Bin movement in progress.
-* Clear FCC bin of ₹10.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Minimalist B12 Repair Complex Face (₹5.2K), Pampers All Round Protection Pant (₹3.8K) and Classic Connect Cigarette (₹1.1K) and match with last GRN qty.
-* W2W audit of aisles D and F as Adjustment is ₹19.0K.</t>
+* Bin movement in progress.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Sanjaynagar</t>
@@ -1497,11 +1309,7 @@
 * Top loss categories: Frozen Food ₹16.5K (36%), Ice Creams &amp; More ₹12.2K (27%), Cigarettes (Paan Corner) ₹3.8K (8%), Fruits &amp; Vegetables ₹2.2K (5%), Hair Care ₹1.7K (4%). Share is of ₹46.1K net loss across loss-making categories.
 * Loss is spread across 963 SKUs and the top 10 make 10% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹6.8K, led by cigarettes ₹4.1K, perfumes ₹2.0K and dry fruits &amp; nuts ₹454.
-* Aisles I and E hold ₹36.0K, 82% of bin-level loss.
-* Clear FCC bin of ₹23.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Shree Akshara Sona Masoori Steam (₹1.6K), Teddyy Baby Pant Style Diaper L 62 (₹1.5K) and Superior MP Wheat Atta, 0% Maida (₹1.5K) and match with last GRN qty.
-* W2W audit of aisles E and G as Adjustment is ₹3.8K.
-* Reconcile RTO ₹732 with LM and STO short receipt ₹1.1K with MH and DH.</t>
+* Aisles I and E hold ₹36.0K, 82% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Richmond Town Network</t>
@@ -1511,10 +1319,7 @@
 * Top loss categories: Dairy, Bread &amp; Eggs ₹5.4K (28%), Ice Creams &amp; More ₹2.5K (13%), Floor &amp; Surface Cleaners (Cleaning Essentials) ₹2.5K (13%), Energy Drink (Cold Drinks &amp; Juices) ₹1.9K (10%), Muesli &amp; Oats (Breakfast &amp; Sauces) ₹1.3K (7%). Share is of ₹19.4K net loss across loss-making categories.
 * Loss is spread across 438 SKUs and the top 10 make 16% of SKU-level loss.
 * Theft-prone SKUs show net loss of ₹2.9K, led by dry fruits &amp; nuts ₹1.8K, cigarettes ₹941 and premium chocolates ₹96.
-* Aisles K and L hold ₹7.7K, 57% of bin-level loss.
-* Clear FCC bin of ₹6.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount FarMart Pantry Premium Roasted (₹1.3K), Monster Energy Ultra Zero Sugar (₹1.0K) and Fortune Refined Sunflower Oil Pouch (₹943) and match with last GRN qty.
-* W2W audit of aisles H and D as Adjustment is ₹23.2K.</t>
+* Aisles K and L hold ₹7.7K, 57% of bin-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹29.8K, mainly from Adjustment ₹15.7K and FCC bin ₹11.1K.
@@ -1523,20 +1328,13 @@
 * Theft-prone SKUs show net loss of ₹7.1K, led by dry fruits &amp; nuts ₹7.1K.
 * Aisles D and E hold ₹49.3K, 87% of bin-level loss.
 * Recurring DHM process adherence gaps.
-* High value negative adjustments every month.
-* Clear FCC bin of ₹11.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.1K shortpick value.
-* Recount Daily Good Cashew Kaju Broken (₹3.4K), GTS Original Kolam Rice (₹2.6K) and GRB Ghee Bottle Pure &amp; Classic (₹1.2K) and match with last GRN qty.
-* W2W audit of aisles D and E as Adjustment is ₹15.7K.</t>
+* High value negative adjustments every month.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹29.2K, mainly from FCC bin ₹16.2K and Adjustment ₹12.6K.
 * Top loss categories: Ice Creams &amp; More ₹10.6K (21%), Dairy, Bread &amp; Eggs ₹9.1K (18%), Cigarettes (Paan Corner) ₹9.1K (18%), Rice &amp; More (Atta, Rice, Oil &amp; Dals) ₹6.4K (13%), Milk Drinks (Cold Drinks &amp; Juices) ₹2.4K (5%). Share is of ₹50.6K net loss across loss-making categories.
 * Loss is spread across 639 SKUs and the top 10 make 24% of SKU-level loss.
-* Theft-prone SKUs show net loss of ₹9.2K, led by cigarettes ₹9.1K and dry fruits &amp; nuts ₹184.
-* Clear FCC bin of ₹16.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Recount Classic Connect Cigarette (₹8.5K), GTS Original Kolam Rice (₹5.1K) and Mother Sparsh Water Baby Wipes (₹2.0K) and match with last GRN qty.
-* W2W audit of aisles C and J as Adjustment is ₹12.6K.</t>
+* Theft-prone SKUs show net loss of ₹9.2K, led by cigarettes ₹9.1K and dry fruits &amp; nuts ₹184.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Dooravani Nagar SS</t>
@@ -1544,9 +1342,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹28.7K, mainly from FCC bin ₹23.4K and RTO loss ₹4.8K.
 * Majority impact is from FCC bin of ₹23.4K. Excluding this, the store is ₹5.2K in loss.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹23.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹4.8K with LM.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">Hosur</t>
@@ -1557,8 +1353,7 @@
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles B and L hold ₹15.7K, 62% of aisle-level loss.
 * DHM not available.
-* 10 crates of excess stock in dry being added back.
-* Clear FCC bin of ₹28.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* 10 crates of excess stock in dry being added back.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Garudachar Palya</t>
@@ -1567,11 +1362,7 @@
     <t xml:space="preserve">* Total IH loss is ₹28.3K, mainly from Adjustment ₹18.9K and FCC bin ₹7.3K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles C and D hold ₹11.3K, 75% of aisle-level loss.
-* Smaller buckets: Other bins ₹1.0K, Shortpick ₹615 and RTO loss ₹501.
-* Clear FCC bin of ₹7.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles C and D as Adjustment is ₹18.9K.
-* Reconcile RTO ₹501 with LM.
-* Close out Other bins stock of ₹1.0K and post it back to inventory.</t>
+* Smaller buckets: Other bins ₹1.0K, Shortpick ₹615 and RTO loss ₹501.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Sarjapur New</t>
@@ -1581,8 +1372,7 @@
 * Majority impact is from FCC bin of ₹32.0K. Excluding this, the store is ₹3.8K positive.
 * Adjustment is a gain of ₹4.5K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and H hold ₹35.9K, 54% of aisle-level loss.
-* Clear FCC bin of ₹32.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles G and H hold ₹35.9K, 54% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BASAVANAPURA</t>
@@ -1590,9 +1380,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹27.5K, mainly from Adjustment ₹16.7K and FCC bin ₹10.2K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and F hold ₹18.6K, 53% of aisle-level loss.
-* Clear FCC bin of ₹10.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles B and E as Adjustment is ₹16.7K.</t>
+* Aisles G and F hold ₹18.6K, 53% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-CV Raman Nagar Network-2</t>
@@ -1601,10 +1389,7 @@
     <t xml:space="preserve">* Total IH loss is ₹27.3K, mainly from Adjustment ₹24.6K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles A and D hold ₹20.1K, 69% of aisle-level loss.
-* Smaller buckets: FCC bin ₹1.4K and RTO loss ₹1.2K.
-* Clear FCC bin of ₹1.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles A and D as Adjustment is ₹24.6K.
-* Reconcile RTO ₹1.2K with LM.</t>
+* Smaller buckets: FCC bin ₹1.4K and RTO loss ₹1.2K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Seegehalli</t>
@@ -1613,11 +1398,7 @@
     <t xml:space="preserve">* Total IH loss is ₹27.3K, mainly from FCC bin ₹11.9K, PO cancel ₹7.4K and Adjustment ₹6.4K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles A and B hold ₹18.5K, 52% of aisle-level loss.
-* Smaller buckets: Shortpick ₹1.4K.
-* Clear FCC bin of ₹11.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.4K shortpick value.
-* W2W audit of aisles A and B as Adjustment is ₹6.4K.
-* Reconcile PO cancel ₹7.4K with procurement and DH.</t>
+* Smaller buckets: Shortpick ₹1.4K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-HBR Layout</t>
@@ -1627,11 +1408,7 @@
 * Majority impact is from FCC bin of ₹18.3K. Excluding this, the store is ₹7.6K in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles J and B hold ₹24.2K, 69% of aisle-level loss.
-* Smaller buckets: Other bins ₹2.1K and RTO loss ₹765.
-* Clear FCC bin of ₹18.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles B and C as Adjustment is ₹4.6K.
-* Reconcile RTO ₹765 with LM.
-* Close out Other bins stock of ₹2.1K and post it back to inventory.</t>
+* Smaller buckets: Other bins ₹2.1K and RTO loss ₹765.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Hennur New</t>
@@ -1640,8 +1417,7 @@
     <t xml:space="preserve">* Total IH loss is ₹25.0K, mainly from Shortpick ₹34.1K.
 * Majority impact is from Shortpick of ₹34.1K. Excluding this, the store is ₹9.1K positive.
 * Adjustment is a gain of ₹9.1K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Cycle count the shortpick bins against the ₹34.1K shortpick value.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-HEBBAL NEW</t>
@@ -1651,9 +1427,7 @@
 * Majority impact is from FCC bin of ₹23.7K. Excluding this, the store is ₹1.1K in loss.
 * Adjustment is a gain of ₹4.5K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Smaller buckets: Shortpick ₹617.
-* Clear FCC bin of ₹23.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹5.1K with LM.</t>
+* Smaller buckets: Shortpick ₹617.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Narayanapura Network</t>
@@ -1662,11 +1436,7 @@
     <t xml:space="preserve">* Total IH loss is ₹22.4K, mainly from Adjustment ₹15.0K and FCC bin ₹5.4K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles F and B hold ₹13.6K, 78% of aisle-level loss.
-* Smaller buckets: STO short receipt ₹1.3K and Other bins ₹580.
-* Clear FCC bin of ₹5.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles B and D as Adjustment is ₹15.0K.
-* Reconcile STO short receipt ₹1.3K with MH and DH.
-* Close out Other bins stock of ₹580 and post it back to inventory.</t>
+* Smaller buckets: STO short receipt ₹1.3K and Other bins ₹580.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Arekere</t>
@@ -1677,10 +1447,7 @@
 * Adjustment is a gain of ₹30.3K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles C and G hold ₹18.8K, 65% of aisle-level loss.
-* Smaller buckets: RTO loss ₹1.3K.
-* Clear FCC bin of ₹19.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹31.3K shortpick value.
-* Reconcile RTO ₹1.3K with LM.</t>
+* Smaller buckets: RTO loss ₹1.3K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Devanahalli</t>
@@ -1688,18 +1455,12 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹21.9K, mainly from Adjustment ₹11.5K and FCC bin ₹8.6K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Smaller buckets: STO short receipt ₹576 and RTO loss ₹538.
-* Clear FCC bin of ₹8.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles E and D as Adjustment is ₹11.5K.
-* Reconcile RTO ₹538 with LM and STO short receipt ₹576 with MH and DH.</t>
+* Smaller buckets: STO short receipt ₹576 and RTO loss ₹538.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹21.9K, mainly from FCC bin ₹13.1K and Adjustment ₹7.1K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Smaller buckets: RTO loss ₹1.7K.
-* Clear FCC bin of ₹13.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles C and H as Adjustment is ₹7.1K.
-* Reconcile RTO ₹1.7K with LM.</t>
+* Smaller buckets: RTO loss ₹1.7K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RWF Yelahanka</t>
@@ -1708,21 +1469,14 @@
     <t xml:space="preserve">* Total IH loss is ₹21.6K, mainly from Adjustment ₹10.3K and FCC bin ₹10.2K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles J and N hold ₹12.4K, 57% of aisle-level loss.
-* Smaller buckets: RTO loss ₹593.
-* Clear FCC bin of ₹10.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles J and K as Adjustment is ₹10.3K.
-* Reconcile RTO ₹593 with LM.</t>
+* Smaller buckets: RTO loss ₹593.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹21.4K, mainly from FCC bin ₹14.7K and RTO loss ₹2.7K.
 * Majority impact is from FCC bin of ₹14.7K. Excluding this, the store is ₹6.7K in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles H and D hold ₹22.9K, 72% of aisle-level loss.
-* Smaller buckets: Shortpick ₹1.9K, PO cancel ₹773, Other bins ₹599 and Adjustment ₹527.
-* Clear FCC bin of ₹14.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.9K shortpick value.
-* Reconcile RTO ₹2.7K with LM and PO cancel ₹773 with procurement and DH.
-* Close out Other bins stock of ₹599 and post it back to inventory.</t>
+* Smaller buckets: Shortpick ₹1.9K, PO cancel ₹773, Other bins ₹599 and Adjustment ₹527.</t>
   </si>
   <si>
     <t xml:space="preserve">planned wall to wall with the sqard  wall to wall was closed  need to do recovery sqard was for recovery </t>
@@ -1740,10 +1494,7 @@
     <t xml:space="preserve">* Total IH loss is ₹20.8K, mainly from Adjustment ₹18.2K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Smaller buckets: FCC bin ₹1.9K and RTO loss ₹735.
-* CCA cross deployed, DH monitoring gap.
-* Clear FCC bin of ₹1.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles B and A as Adjustment is ₹18.2K.
-* Reconcile RTO ₹735 with LM.</t>
+* CCA cross deployed, DH monitoring gap.</t>
   </si>
   <si>
     <t xml:space="preserve">20K</t>
@@ -1755,11 +1506,7 @@
     <t xml:space="preserve">* Total IH loss is ₹20.0K, mainly from FCC bin ₹9.5K and Adjustment ₹8.4K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles K and E hold ₹11.2K, 54% of aisle-level loss.
-* Smaller buckets: Other bins ₹1.5K and RTO loss ₹589.
-* Clear FCC bin of ₹9.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles E and B as Adjustment is ₹8.4K.
-* Reconcile RTO ₹589 with LM.
-* Close out Other bins stock of ₹1.5K and post it back to inventory.</t>
+* Smaller buckets: Other bins ₹1.5K and RTO loss ₹589.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bellandur-3</t>
@@ -1767,10 +1514,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹19.5K, mainly from FCC bin ₹9.9K, Adjustment ₹7.3K and Shortpick ₹2.1K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and H hold ₹49.7K, 64% of aisle-level loss.
-* Clear FCC bin of ₹9.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.1K shortpick value.
-* W2W audit of aisles E and B as Adjustment is ₹7.3K.</t>
+* Aisles I and H hold ₹49.7K, 64% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BASAVANAPURA SS</t>
@@ -1779,10 +1523,7 @@
     <t xml:space="preserve">* Total IH loss is ₹19.1K, mainly from FCC bin ₹11.3K and Adjustment ₹6.9K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles D and F hold ₹5.1K, 60% of aisle-level loss.
-* Smaller buckets: RTO loss ₹876.
-* Clear FCC bin of ₹11.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles F and BASV as Adjustment is ₹6.9K.
-* Reconcile RTO ₹876 with LM.</t>
+* Smaller buckets: RTO loss ₹876.</t>
   </si>
   <si>
     <t xml:space="preserve">Kochi</t>
@@ -1799,10 +1540,7 @@
 * Adjustment is a gain of ₹14.1K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles F and A hold ₹5.5K, 55% of aisle-level loss.
-* Smaller buckets: Other bins ₹1.8K.
-* Clear FCC bin of ₹14.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile STO short receipt ₹15.5K with MH and DH.
-* Close out Other bins stock of ₹1.8K and post it back to inventory.</t>
+* Smaller buckets: Other bins ₹1.8K.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Kalamassery SS</t>
@@ -1811,8 +1549,7 @@
     <t xml:space="preserve">* Total IH loss is ₹17.4K, mainly from FCC bin ₹17.3K.
 * Majority impact is from FCC bin of ₹17.3K. Excluding this, the store is ₹122 in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and G hold ₹7.6K, 55% of aisle-level loss.
-* Clear FCC bin of ₹17.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles B and G hold ₹7.6K, 55% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-JC Nagar</t>
@@ -1820,8 +1557,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹16.5K, mainly from Shortpick ₹16.4K.
 * Majority impact is from Shortpick of ₹16.4K. Excluding this, the store is ₹84 in loss.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Cycle count the shortpick bins against the ₹16.4K shortpick value.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Shivaji nagar New</t>
@@ -1832,9 +1568,7 @@
 * Adjustment is a gain of ₹2.7K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles M and L hold ₹17.4K, 64% of aisle-level loss.
-* Smaller buckets: RTO loss ₹1.6K and STO short receipt ₹1.6K.
-* Clear FCC bin of ₹15.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.6K with LM and STO short receipt ₹1.6K with MH and DH.</t>
+* Smaller buckets: RTO loss ₹1.6K and STO short receipt ₹1.6K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Nehru Nagar SS</t>
@@ -1845,8 +1579,7 @@
 * Adjustment is a gain of ₹2.0K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles A and ART hold ₹4.6K, 75% of aisle-level loss.
-* Smaller buckets: RTO loss ₹523.
-* Reconcile RTO ₹523 with LM and STO short receipt ₹17.6K with MH and DH.</t>
+* Smaller buckets: RTO loss ₹523.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Nikoo home SS</t>
@@ -1854,9 +1587,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹16.0K, mainly from FCC bin ₹14.2K and RTO loss ₹1.7K.
 * Majority impact is from FCC bin of ₹14.2K. Excluding this, the store is ₹1.8K in loss.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹14.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.7K with LM.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹15.5K, mainly from RTO loss ₹7.3K, STO short receipt ₹5.8K and FCC bin ₹5.1K.
@@ -1864,9 +1595,7 @@
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles G and H hold ₹28.2K, 57% of aisle-level loss.
 * DHM monitoring gap, assigned DHM absconded.
-* Banashankari DHM deployed temporarily.
-* Clear FCC bin of ₹5.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹7.3K with LM and STO short receipt ₹5.8K with MH and DH.</t>
+* Banashankari DHM deployed temporarily.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Peenya New</t>
@@ -1875,10 +1604,7 @@
     <t xml:space="preserve">* Total IH loss is ₹15.1K, mainly from Adjustment ₹12.1K and FCC bin ₹1.8K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles K and J hold ₹14.3K, 61% of aisle-level loss.
-* Smaller buckets: RTO loss ₹1.1K.
-* Clear FCC bin of ₹1.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles A and B as Adjustment is ₹12.1K.
-* Reconcile RTO ₹1.1K with LM.</t>
+* Smaller buckets: RTO loss ₹1.1K.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹14.7K, mainly from Shortpick ₹11.1K and RTO loss ₹3.7K.
@@ -1887,10 +1613,7 @@
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles N and C hold ₹8.1K, 51% of aisle-level loss.
 * Smaller buckets: FCC bin ₹1.3K.
-* RC wrong shot picking identified by DHM.
-* Clear FCC bin of ₹1.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹11.1K shortpick value.
-* Reconcile RTO ₹3.7K with LM.</t>
+* RC wrong shot picking identified by DHM.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Sompura</t>
@@ -1899,19 +1622,13 @@
     <t xml:space="preserve">* Total IH loss is ₹14.7K, mainly from Adjustment ₹10.1K and STO short receipt ₹3.0K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles O and D hold ₹26.2K, 83% of aisle-level loss.
-* Smaller buckets: FCC bin ₹1.1K.
-* Clear FCC bin of ₹1.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles D and H as Adjustment is ₹10.1K.
-* Reconcile STO short receipt ₹3.0K with MH and DH.</t>
+* Smaller buckets: FCC bin ₹1.1K.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹13.6K, mainly from FCC bin ₹8.1K, Adjustment ₹2.2K and Shortpick ₹1.6K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles L and B hold ₹6.0K, 53% of aisle-level loss.
-* FCC apple to apple reconciliation done, ₹6K identified.
-* Clear FCC bin of ₹8.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.6K shortpick value.
-* Reconcile STO short receipt ₹1.5K with MH and DH.</t>
+* FCC apple to apple reconciliation done, ₹6K identified.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bagalur</t>
@@ -1922,10 +1639,7 @@
 * Adjustment is a gain of ₹6.7K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles C and E hold ₹11.4K, 57% of aisle-level loss.
-* Smaller buckets: RTO loss ₹1.1K and Other bins ₹928.
-* Clear FCC bin of ₹16.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.1K with LM.
-* Close out Other bins stock of ₹928 and post it back to inventory.</t>
+* Smaller buckets: RTO loss ₹1.1K and Other bins ₹928.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Singasandra SS</t>
@@ -1935,9 +1649,7 @@
 * Majority impact is from FCC bin of ₹12.7K. Excluding this, the store is ₹773 positive.
 * Adjustment is a gain of ₹2.1K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and R hold ₹12.4K, 51% of aisle-level loss.
-* Clear FCC bin of ₹12.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.3K with LM.</t>
+* Aisles D and R hold ₹12.4K, 51% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Singapura</t>
@@ -1947,8 +1659,7 @@
 * Majority impact is from FCC bin of ₹14.1K. Excluding this, the store is ₹2.5K positive.
 * Adjustment is a gain of ₹2.7K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and H hold ₹10.8K, 64% of aisle-level loss.
-* Clear FCC bin of ₹14.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles A and H hold ₹10.8K, 64% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Edappally</t>
@@ -1957,10 +1668,7 @@
     <t xml:space="preserve">* Total IH loss is ₹11.3K, mainly from FCC bin ₹8.2K and Shortpick ₹1.4K.
 * Majority impact is from FCC bin of ₹8.2K. Excluding this, the store is ₹3.2K in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Smaller buckets: Adjustment ₹1.0K and RTO loss ₹507.
-* Clear FCC bin of ₹8.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.4K shortpick value.
-* Reconcile RTO ₹507 with LM.</t>
+* Smaller buckets: Adjustment ₹1.0K and RTO loss ₹507.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Marathahalli New</t>
@@ -1970,9 +1678,7 @@
 * Majority impact is from FCC bin of ₹19.0K. Excluding this, the store is ₹8.0K positive.
 * Adjustment is a gain of ₹14.9K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Smaller buckets: Shortpick ₹873.
-* Clear FCC bin of ₹19.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹3.5K with LM and STO short receipt ₹2.5K with MH and DH.</t>
+* Smaller buckets: Shortpick ₹873.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BTM Layout Network-3</t>
@@ -1982,9 +1688,7 @@
 * Majority impact is from FCC bin of ₹39.4K. Excluding this, the store is ₹28.5K positive.
 * Adjustment is a gain of ₹29.9K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Smaller buckets: RTO loss ₹1.1K.
-* Clear FCC bin of ₹39.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.1K with LM.</t>
+* Smaller buckets: RTO loss ₹1.1K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Mico layout network-2</t>
@@ -1995,8 +1699,7 @@
 * Adjustment is a gain of ₹2.6K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles F and K hold ₹5.1K, 56% of aisle-level loss.
-* Smaller buckets: Shortpick ₹815.
-* Clear FCC bin of ₹11.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Smaller buckets: Shortpick ₹815.</t>
   </si>
   <si>
     <t xml:space="preserve">Belgavi</t>
@@ -2007,9 +1710,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹9.5K, mainly from Adjustment ₹4.7K and FCC bin ₹4.4K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Putaway deviation.
-* Clear FCC bin of ₹4.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles A and J as Adjustment is ₹4.7K.</t>
+* Putaway deviation.</t>
   </si>
   <si>
     <t xml:space="preserve">15K</t>
@@ -2022,8 +1723,7 @@
 * Majority impact is from STO short receipt of ₹8.9K. Excluding this, the store is ₹620 in loss.
 * Adjustment is a gain of ₹1.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles K and I hold ₹3.2K, 72% of aisle-level loss.
-* Reconcile RTO ₹2.0K with LM and STO short receipt ₹8.9K with MH and DH.</t>
+* Aisles K and I hold ₹3.2K, 72% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Chikkanagamangala</t>
@@ -2033,9 +1733,7 @@
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * 4 IBAs involved in theft (cigarettes and HV SKUs).
 * SLP asked FR partner to hold salary, investigation in progress.
-* SLP recovery ₹25,000.
-* Clear FCC bin of ₹3.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles A and C as Adjustment is ₹5.4K.</t>
+* SLP recovery ₹25,000.</t>
   </si>
   <si>
     <t xml:space="preserve">SLP Investigation is under progress</t>
@@ -2048,9 +1746,7 @@
 * Majority impact is from FCC bin of ₹11.4K. Excluding this, the store is ₹2.5K positive.
 * Adjustment is a gain of ₹8.7K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and M hold ₹12.3K, 76% of aisle-level loss.
-* Clear FCC bin of ₹11.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹6.2K with LM.</t>
+* Aisles I and M hold ₹12.3K, 76% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Doddakannelli SS</t>
@@ -2060,9 +1756,7 @@
 * Majority impact is from FCC bin of ₹6.5K. Excluding this, the store is ₹2.3K in loss.
 * Adjustment is a gain of ₹2.0K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and E hold ₹6.8K, 73% of aisle-level loss.
-* Clear FCC bin of ₹6.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹4.0K with LM.</t>
+* Aisles D and E hold ₹6.8K, 73% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Kalamassery</t>
@@ -2073,10 +1767,7 @@
 * Adjustment is a gain of ₹3.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles B and D hold ₹10.0K, 54% of aisle-level loss.
-* Smaller buckets: Other bins ₹748 and RTO loss ₹535.
-* Clear FCC bin of ₹10.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹535 with LM.
-* Close out Other bins stock of ₹748 and post it back to inventory.</t>
+* Smaller buckets: Other bins ₹748 and RTO loss ₹535.</t>
   </si>
   <si>
     <t xml:space="preserve">Mysuru</t>
@@ -2090,34 +1781,27 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹8.7K, mainly from Adjustment ₹8.1K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles E and K hold ₹14.9K, 57% of aisle-level loss.
-* W2W audit of aisles K and C as Adjustment is ₹8.1K.</t>
+* Aisles E and K hold ₹14.9K, 57% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kasturinagar New</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹8.2K, mainly from Adjustment ₹5.4K and FCC bin ₹2.7K.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹2.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles P and B as Adjustment is ₹5.4K.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹7.7K, mainly from FCC bin ₹3.9K and Adjustment ₹3.8K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles M and C hold ₹13.5K, 89% of aisle-level loss.
-* Freezer stock mixed up, wrong adjustment due to wrong putaway.
-* Clear FCC bin of ₹3.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles C and A as Adjustment is ₹3.8K.</t>
+* Freezer stock mixed up, wrong adjustment due to wrong putaway.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹7.5K, mainly from FCC bin ₹7.0K and RTO loss ₹970.
 * Majority impact is from FCC bin of ₹7.0K. Excluding this, the store is ₹489 in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles J and F hold ₹8.3K, 56% of aisle-level loss.
-* Wrong putaway by LC1 IBAs.
-* Clear FCC bin of ₹7.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹970 with LM.</t>
+* Wrong putaway by LC1 IBAs.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Marathahalli-4</t>
@@ -2127,8 +1811,7 @@
 * Majority impact is from FCC bin of ₹8.4K. Excluding this, the store is ₹1.0K positive.
 * Adjustment is a gain of ₹2.1K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and A hold ₹10.1K, 66% of aisle-level loss.
-* Clear FCC bin of ₹8.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles I and A hold ₹10.1K, 66% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bannerghatta SS</t>
@@ -2138,10 +1821,7 @@
 * Majority impact is from FCC bin of ₹14.7K. Excluding this, the store is ₹7.4K positive.
 * Adjustment is a gain of ₹10.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles N and M hold ₹10.1K, 51% of aisle-level loss.
-* Clear FCC bin of ₹14.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.1K shortpick value.
-* Reconcile RTO ₹2.0K with LM.</t>
+* Aisles N and M hold ₹10.1K, 51% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Tippenahalli</t>
@@ -2152,9 +1832,7 @@
 * Adjustment is a gain of ₹1.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles C and D hold ₹16.5K, 61% of aisle-level loss.
-* Smaller buckets: RTO loss ₹573.
-* Clear FCC bin of ₹8.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹573 with LM.</t>
+* Smaller buckets: RTO loss ₹573.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Budigere Cross</t>
@@ -2163,10 +1841,7 @@
     <t xml:space="preserve">* Total IH loss is ₹7.1K, mainly from Adjustment ₹5.7K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles G and H hold ₹11.5K, 65% of aisle-level loss.
-* Smaller buckets: FCC bin ₹629 and RTO loss ₹590.
-* Clear FCC bin of ₹629 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles C and E as Adjustment is ₹5.7K.
-* Reconcile RTO ₹590 with LM.</t>
+* Smaller buckets: FCC bin ₹629 and RTO loss ₹590.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RK Hegde Nagar</t>
@@ -2174,9 +1849,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹6.9K, mainly from FCC bin ₹3.1K, STO short receipt ₹2.8K and Adjustment ₹805.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and E hold ₹7.3K, 73% of aisle-level loss.
-* Clear FCC bin of ₹3.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile STO short receipt ₹2.8K with MH and DH.</t>
+* Aisles I and E hold ₹7.3K, 73% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RAGHAVENDRA LAYOUT</t>
@@ -2186,9 +1859,7 @@
 * Majority impact is from Shortpick of ₹7.0K. Excluding this, the store is ₹287 positive.
 * Adjustment is a gain of ₹5.8K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and A hold ₹7.9K, 77% of aisle-level loss.
-* Clear FCC bin of ₹5.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹7.0K shortpick value.</t>
+* Aisles B and A hold ₹7.9K, 77% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Hegganahalli</t>
@@ -2196,16 +1867,13 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹6.5K, mainly from Adjustment ₹5.7K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles J and H hold ₹15.6K, 83% of aisle-level loss.
-* W2W audit of aisles G and D as Adjustment is ₹5.7K.</t>
+* Aisles J and H hold ₹15.6K, 83% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹6.4K, mainly from FCC bin ₹3.4K, Shortpick ₹1.3K and Adjustment ₹1.2K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles F and E hold ₹4.3K, 54% of aisle-level loss.
-* Wrong putaway by LC1 IBAs.
-* Clear FCC bin of ₹3.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.3K shortpick value.</t>
+* Wrong putaway by LC1 IBAs.</t>
   </si>
   <si>
     <t xml:space="preserve">Ravishankar gowda</t>
@@ -2216,8 +1884,7 @@
 * Adjustment is a gain of ₹1.6K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles M and L hold ₹10.4K, 75% of aisle-level loss.
-* CCA delta, 3 CCAs now hired.
-* Clear FCC bin of ₹6.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* CCA delta, 3 CCAs now hired.</t>
   </si>
   <si>
     <t xml:space="preserve">10K</t>
@@ -2225,9 +1892,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹5.9K, mainly from Adjustment ₹3.7K and FCC bin ₹2.1K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* CCA cross deployed, DH monitoring gap.
-* Clear FCC bin of ₹2.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* W2W audit of aisles C and I as Adjustment is ₹3.7K.</t>
+* CCA cross deployed, DH monitoring gap.</t>
   </si>
   <si>
     <t xml:space="preserve">9K</t>
@@ -2244,9 +1909,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹5.5K, mainly from Adjustment ₹4.2K and RTO loss ₹666.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and B hold ₹4.6K, 60% of aisle-level loss.
-* W2W audit of aisles A and B as Adjustment is ₹4.2K.
-* Reconcile RTO ₹666 with LM.</t>
+* Aisles A and B hold ₹4.6K, 60% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Yelenahalli</t>
@@ -2256,16 +1919,14 @@
 * Majority impact is from FCC bin of ₹6.1K. Excluding this, the store is ₹753 positive.
 * Adjustment is a gain of ₹1.6K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and D hold ₹10.7K, 83% of aisle-level loss.
-* Clear FCC bin of ₹6.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles A and D hold ₹10.7K, 83% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹5.2K, mainly from FCC bin ₹3.8K and Adjustment ₹1.1K.
 * Majority impact is from FCC bin of ₹3.8K. Excluding this, the store is ₹1.4K in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
 * Aisles C and K hold ₹11.5K, 62% of aisle-level loss.
-* Putaway deviation, floor not handed over to next shift.
-* Clear FCC bin of ₹3.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Putaway deviation, floor not handed over to next shift.</t>
   </si>
   <si>
     <t xml:space="preserve">7K</t>
@@ -2278,8 +1939,7 @@
 * Majority impact is from FCC bin of ₹6.8K. Excluding this, the store is ₹1.9K positive.
 * Adjustment is a gain of ₹3.0K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles E and A hold ₹7.2K, 86% of aisle-level loss.
-* Clear FCC bin of ₹6.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles E and A hold ₹7.2K, 86% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BANNERGHATTA</t>
@@ -2289,8 +1949,7 @@
 * Majority impact is from FCC bin of ₹8.2K. Excluding this, the store is ₹3.6K positive.
 * Adjustment is a gain of ₹3.6K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and E hold ₹6.2K, 68% of aisle-level loss.
-* Clear FCC bin of ₹8.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles D and E hold ₹6.2K, 68% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Pipeline road new</t>
@@ -2300,8 +1959,7 @@
 * Majority impact is from FCC bin of ₹11.5K. Excluding this, the store is ₹7.1K positive.
 * Adjustment is a gain of ₹7.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and L hold ₹10.0K, 56% of aisle-level loss.
-* Clear FCC bin of ₹11.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles I and L hold ₹10.0K, 56% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Doddanekundi</t>
@@ -2310,8 +1968,7 @@
     <t xml:space="preserve">* Total IH loss is ₹4.4K, mainly from FCC bin ₹6.5K.
 * Majority impact is from FCC bin of ₹6.5K. Excluding this, the store is ₹2.1K positive.
 * Adjustment is a gain of ₹2.3K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹6.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Thengod</t>
@@ -2320,8 +1977,7 @@
     <t xml:space="preserve">* Total IH loss is ₹4.3K, mainly from FCC bin ₹9.5K.
 * Majority impact is from FCC bin of ₹9.5K. Excluding this, the store is ₹5.1K positive.
 * Adjustment is a gain of ₹5.1K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹9.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Cholayanakanalli</t>
@@ -2331,9 +1987,7 @@
 * Majority impact is from FCC bin of ₹9.5K. Excluding this, the store is ₹5.3K positive.
 * Adjustment is a gain of ₹7.3K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles P and O hold ₹34.6K, 69% of aisle-level loss.
-* Clear FCC bin of ₹9.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹2.0K with LM.</t>
+* Aisles P and O hold ₹34.6K, 69% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Sundarapuram</t>
@@ -2341,8 +1995,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹4.2K, mainly from Adjustment ₹2.8K and FCC bin ₹1.1K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and F hold ₹6.0K, 66% of aisle-level loss.
-* Clear FCC bin of ₹1.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles A and F hold ₹6.0K, 66% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bellandur new</t>
@@ -2352,10 +2005,7 @@
 * Majority impact is from FCC bin of ₹7.1K. Excluding this, the store is ₹3.2K positive.
 * Adjustment is a gain of ₹6.6K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and D hold ₹4.3K, 98% of aisle-level loss.
-* Clear FCC bin of ₹7.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹2.2K shortpick value.
-* Close out Other bins stock of ₹1.3K and post it back to inventory.</t>
+* Aisles G and D hold ₹4.3K, 98% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Channasandra</t>
@@ -2365,9 +2015,7 @@
 * Majority impact is from FCC bin of ₹3.2K. Excluding this, the store is ₹447 in loss.
 * Adjustment is a gain of ₹1.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and G hold ₹20.8K, 84% of aisle-level loss.
-* Clear FCC bin of ₹3.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.8K shortpick value.</t>
+* Aisles I and G hold ₹20.8K, 84% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-PALLURTHY</t>
@@ -2376,16 +2024,14 @@
     <t xml:space="preserve">* Total IH loss is ₹3.4K, mainly from FCC bin ₹2.8K and Adjustment ₹632.
 * Majority impact is from FCC bin of ₹2.8K. Excluding this, the store is ₹632 in loss.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and K hold ₹12.6K, 84% of aisle-level loss.
-* Clear FCC bin of ₹2.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles H and K hold ₹12.6K, 84% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Hudco</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹3.4K, mainly from Adjustment ₹3.3K.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* W2W audit of aisles H and B as Adjustment is ₹3.3K.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Anjanapura</t>
@@ -2401,8 +2047,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹2.8K, mainly from Adjustment ₹1.6K, FCC bin ₹792 and RTO loss ₹426.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and I hold ₹5.5K, 74% of aisle-level loss.
-* Clear FCC bin of ₹792 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles H and I hold ₹5.5K, 74% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RICHMOND TOWN</t>
@@ -2412,9 +2057,7 @@
 * Majority impact is from FCC bin of ₹18.1K. Excluding this, the store is ₹15.4K positive.
 * Adjustment is a gain of ₹17.7K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and L hold ₹14.7K, 56% of aisle-level loss.
-* Clear FCC bin of ₹18.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.9K shortpick value.</t>
+* Aisles G and L hold ₹14.7K, 56% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Marathahalli 2</t>
@@ -2424,8 +2067,7 @@
 * Majority impact is from FCC bin of ₹7.7K. Excluding this, the store is ₹5.0K positive.
 * Adjustment is a gain of ₹5.3K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and F hold ₹8.8K, 83% of aisle-level loss.
-* Clear FCC bin of ₹7.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles D and F hold ₹8.8K, 83% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Peenya Network</t>
@@ -2433,8 +2075,7 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹2.3K, mainly from Adjustment ₹1.5K and RTO loss ₹658.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and H hold ₹3.8K, 65% of aisle-level loss.
-* Reconcile RTO ₹658 with LM.</t>
+* Aisles B and H hold ₹3.8K, 65% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">Tumkuru</t>
@@ -2445,16 +2086,14 @@
   <si>
     <t xml:space="preserve">* Total IH loss is ₹2.3K, mainly from Adjustment ₹1.8K and FCC bin ₹511.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and A hold ₹3.6K, 67% of aisle-level loss.
-* Clear FCC bin of ₹511 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles H and A hold ₹3.6K, 67% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">* Total IH loss is ₹2.0K, mainly from FCC bin ₹4.0K.
 * Majority impact is from FCC bin of ₹4.0K. Excluding this, the store is ₹2.0K positive.
 * Adjustment is a gain of ₹2.0K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles M and K hold ₹12.3K, 80% of aisle-level loss.
-* Clear FCC bin of ₹4.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles M and K hold ₹12.3K, 80% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">5K</t>
@@ -2467,8 +2106,7 @@
 * Majority impact is from FCC bin of ₹6.4K. Excluding this, the store is ₹4.6K positive.
 * Adjustment is a gain of ₹5.0K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles N and D hold ₹4.2K, 73% of aisle-level loss.
-* Clear FCC bin of ₹6.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles N and D hold ₹4.2K, 73% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-HSR SS</t>
@@ -2477,8 +2115,7 @@
     <t xml:space="preserve">* Total IH loss is ₹1.8K, mainly from FCC bin ₹22.6K.
 * Majority impact is from FCC bin of ₹22.6K. Excluding this, the store is ₹20.8K positive.
 * Adjustment is a gain of ₹20.8K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹22.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Parashakti nagar</t>
@@ -2488,8 +2125,7 @@
 * Majority impact is from FCC bin of ₹4.7K. Excluding this, the store is ₹3.0K positive.
 * Adjustment is a gain of ₹3.1K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and C hold ₹4.8K, 69% of aisle-level loss.
-* Clear FCC bin of ₹4.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles A and C hold ₹4.8K, 69% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Silver County</t>
@@ -2498,10 +2134,7 @@
     <t xml:space="preserve">* Total IH loss is ₹1.5K, mainly from FCC bin ₹4.4K, STO short receipt ₹3.8K and Shortpick ₹3.0K.
 * Majority impact is from FCC bin of ₹4.4K. Excluding this, the store is ₹2.9K positive.
 * Adjustment is a gain of ₹9.9K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹4.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹3.0K shortpick value.
-* Reconcile STO short receipt ₹3.8K with MH and DH.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bellandur SS</t>
@@ -2511,8 +2144,7 @@
 * Majority impact is from FCC bin of ₹11.3K. Excluding this, the store is ₹10.2K positive.
 * Adjustment is a gain of ₹10.4K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles BAT and H hold ₹6.7K, 59% of aisle-level loss.
-* Clear FCC bin of ₹11.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles BAT and H hold ₹6.7K, 59% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Fort</t>
@@ -2521,8 +2153,7 @@
     <t xml:space="preserve">* Total IH loss is ₹1.0K, mainly from FCC bin ₹1.2K and Shortpick ₹183.
 * Majority impact is from FCC bin of ₹1.2K. Excluding this, the store is ₹151 positive.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles Unknown and Q hold ₹2.9K, 52% of aisle-level loss.
-* Clear FCC bin of ₹1.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.</t>
+* Aisles Unknown and Q hold ₹2.9K, 52% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Golahalli</t>
@@ -2531,9 +2162,7 @@
     <t xml:space="preserve">* Total IH loss is ₹711, mainly from FCC bin ₹2.7K, Other bins ₹2.5K and RTO loss ₹391.
 * Majority impact is from FCC bin of ₹2.7K. Excluding this, the store is ₹1.9K positive.
 * Adjustment is a gain of ₹5.1K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹2.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Close out Other bins stock of ₹2.5K and post it back to inventory.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-HeadOffice-Cafe</t>
@@ -2553,8 +2182,7 @@
 * Majority impact is from RTO loss of ₹7.3K. Excluding this, the store is ₹6.7K positive.
 * Adjustment is a gain of ₹6.7K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles K and H hold ₹2.9K, 55% of aisle-level loss.
-* Reconcile RTO ₹7.3K with LM.</t>
+* Aisles K and H hold ₹2.9K, 55% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Electronic City SS</t>
@@ -2564,9 +2192,7 @@
 * Majority impact is from FCC bin of ₹4.7K. Excluding this, the store is ₹4.2K positive.
 * Adjustment is a gain of ₹6.2K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles U and N hold ₹5.8K, 71% of aisle-level loss.
-* Clear FCC bin of ₹4.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹2.0K with LM.</t>
+* Aisles U and N hold ₹5.8K, 71% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Bogadi</t>
@@ -2593,10 +2219,7 @@
 * Majority impact is from RTO loss of ₹1.0K. Excluding this, the store is ₹845 positive.
 * Adjustment is a gain of ₹2.3K, which offsets part of the loss in other buckets.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and C hold ₹3.1K, 59% of aisle-level loss.
-* Clear FCC bin of ₹645 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.0K with LM.
-* Close out Other bins stock of ₹786 and post it back to inventory.</t>
+* Aisles B and C hold ₹3.1K, 59% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BTM LAYOUT NEW</t>
@@ -2605,17 +2228,13 @@
     <t xml:space="preserve">* Total IH loss is ₹34, mainly from FCC bin ₹11.1K, Shortpick ₹9.3K and RTO loss ₹2.2K.
 * Majority impact is from FCC bin of ₹11.1K. Excluding this, the store is ₹11.0K positive.
 * Adjustment is a gain of ₹22.6K, which offsets part of the loss in other buckets.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹11.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹9.3K shortpick value.
-* Reconcile RTO ₹2.2K with LM.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BTM-2</t>
   </si>
   <si>
-    <t xml:space="preserve">* No IH loss booked for the period across any bucket.
-* No recovery action needed. Continue daily cycle count as per plan.</t>
+    <t xml:space="preserve">* No IH loss booked for the period across any bucket.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Vidyaranyapura</t>
@@ -2638,9 +2257,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹240 because of adjustment gains of ₹1.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹956 and RTO loss ₹283.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹956 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹1.5K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BEL-Sector 12</t>
@@ -2648,9 +2265,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹264 because of adjustment gains of ₹1.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.5K and RTO loss ₹129.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹1.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹1.9K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kasavanahalli</t>
@@ -2659,10 +2274,7 @@
     <t xml:space="preserve">* Store is net positive by ₹358 because of adjustment gains of ₹4.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: STO short receipt ₹1.4K, FCC bin ₹1.3K, RTO loss ₹1.1K and Shortpick ₹43.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles M and K hold ₹2.6K, 90% of aisle-level loss.
-* Clear FCC bin of ₹1.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.1K with LM and STO short receipt ₹1.4K with MH and DH.
-* Validate adjustment gains of ₹4.2K against GRN and STO inward before month close.</t>
+* Aisles M and K hold ₹2.6K, 90% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Carmelaram</t>
@@ -2670,12 +2282,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹465 because of adjustment gains of ₹13.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Shortpick ₹6.0K, FCC bin ₹4.8K, Other bins ₹1.6K and RTO loss ₹543.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹4.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹6.0K shortpick value.
-* Reconcile RTO ₹543 with LM.
-* Close out Other bins stock of ₹1.6K and post it back to inventory.
-* Validate adjustment gains of ₹13.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">Kozhikode</t>
@@ -2685,8 +2292,7 @@
   </si>
   <si>
     <t xml:space="preserve">* Store is net positive by ₹599 because of adjustment gains of ₹599. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹599 against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Devasandra Extension</t>
@@ -2695,10 +2301,7 @@
     <t xml:space="preserve">* Store is net positive by ₹638 because of adjustment gains of ₹9.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: STO short receipt ₹4.3K, FCC bin ₹3.9K and RTO loss ₹652.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and B hold ₹7.2K, 71% of aisle-level loss.
-* Clear FCC bin of ₹3.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹652 with LM and STO short receipt ₹4.3K with MH and DH.
-* Validate adjustment gains of ₹9.5K against GRN and STO inward before month close.</t>
+* Aisles G and B hold ₹7.2K, 71% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bommasandra</t>
@@ -2707,10 +2310,7 @@
     <t xml:space="preserve">* Store is net positive by ₹809 because of adjustment gains of ₹15.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹12.3K, Shortpick ₹902, RTO loss ₹744 and Other bins ₹428.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles K and A hold ₹4.6K, 59% of aisle-level loss.
-* Clear FCC bin of ₹12.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹744 with LM.
-* Validate adjustment gains of ₹15.2K against GRN and STO inward before month close.</t>
+* Aisles K and A hold ₹4.6K, 59% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RR Nagar SS</t>
@@ -2718,10 +2318,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹819 because of adjustment gains of ₹14.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹12.9K and RTO loss ₹741.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹12.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹741 with LM.
-* Validate adjustment gains of ₹14.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Teachers colony</t>
@@ -2730,10 +2327,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.1K because of adjustment gains of ₹8.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.5K and RTO loss ₹841.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles P and G hold ₹2.1K, 72% of aisle-level loss.
-* Clear FCC bin of ₹6.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹841 with LM.
-* Validate adjustment gains of ₹8.4K against GRN and STO inward before month close.</t>
+* Aisles P and G hold ₹2.1K, 72% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Hope Farm SS</t>
@@ -2742,10 +2336,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.2K because of adjustment gains of ₹4.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹1.7K, FCC bin ₹1.6K and Shortpick ₹69.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles P09 and P15 hold ₹3.0K, 58% of aisle-level loss.
-* Clear FCC bin of ₹1.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.7K with LM.
-* Validate adjustment gains of ₹4.6K against GRN and STO inward before month close.</t>
+* Aisles P09 and P15 hold ₹3.0K, 58% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Sattava East SS</t>
@@ -2753,10 +2344,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹1.3K because of adjustment gains of ₹5.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.3K and RTO loss ₹1.8K.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹2.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.8K with LM.
-* Validate adjustment gains of ₹5.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Doomasandra</t>
@@ -2765,11 +2353,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.3K because of adjustment gains of ₹12.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: STO short receipt ₹5.3K, Shortpick ₹4.0K, FCC bin ₹954 and RTO loss ₹268.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles K and E hold ₹5.2K, 70% of aisle-level loss.
-* Clear FCC bin of ₹954 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹4.0K shortpick value.
-* Reconcile STO short receipt ₹5.3K with MH and DH.
-* Validate adjustment gains of ₹12.1K against GRN and STO inward before month close.</t>
+* Aisles K and E hold ₹5.2K, 70% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-R S Puram</t>
@@ -2777,9 +2361,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹1.3K because of adjustment gains of ₹2.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.1K and RTO loss ₹39.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹1.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹2.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Neo Town</t>
@@ -2787,8 +2369,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹1.5K because of adjustment gains of ₹1.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹23.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹1.5K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">Davanagere</t>
@@ -2800,10 +2381,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.6K because of adjustment gains of ₹17.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹8.7K, STO short receipt ₹7.2K and RTO loss ₹545.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles J and C hold ₹1.6K, 63% of aisle-level loss.
-* Clear FCC bin of ₹8.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹545 with LM and STO short receipt ₹7.2K with MH and DH.
-* Validate adjustment gains of ₹17.9K against GRN and STO inward before month close.</t>
+* Aisles J and C hold ₹1.6K, 63% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RR Nagar Network</t>
@@ -2812,9 +2390,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.9K because of adjustment gains of ₹12.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹9.9K, RTO loss ₹321, STO short receipt ₹165 and Shortpick ₹129.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and H hold ₹8.2K, 75% of aisle-level loss.
-* Clear FCC bin of ₹9.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹12.4K against GRN and STO inward before month close.</t>
+* Aisles B and H hold ₹8.2K, 75% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Yelahanka new town New</t>
@@ -2823,11 +2399,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.9K because of adjustment gains of ₹8.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.1K, Shortpick ₹1.6K and STO short receipt ₹1.5K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and H hold ₹3.1K, 86% of aisle-level loss.
-* Clear FCC bin of ₹3.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹1.6K shortpick value.
-* Reconcile STO short receipt ₹1.5K with MH and DH.
-* Validate adjustment gains of ₹8.1K against GRN and STO inward before month close.</t>
+* Aisles C and H hold ₹3.1K, 86% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BTM-3</t>
@@ -2836,10 +2408,7 @@
     <t xml:space="preserve">* Store is net positive by ₹1.9K because of adjustment gains of ₹12.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹9.7K and RTO loss ₹559.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and E hold ₹6.8K, 72% of aisle-level loss.
-* Clear FCC bin of ₹9.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹559 with LM.
-* Validate adjustment gains of ₹12.2K against GRN and STO inward before month close.</t>
+* Aisles I and E hold ₹6.8K, 72% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Vadavalli 1</t>
@@ -2848,9 +2417,7 @@
     <t xml:space="preserve">* Store is net positive by ₹2.0K because of adjustment gains of ₹2.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Other bins ₹896.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and G hold ₹2.4K, 87% of aisle-level loss.
-* Close out Other bins stock of ₹896 and post it back to inventory.
-* Validate adjustment gains of ₹2.9K against GRN and STO inward before month close.</t>
+* Aisles I and G hold ₹2.4K, 87% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">DEV-Jayanagara</t>
@@ -2859,9 +2426,7 @@
     <t xml:space="preserve">* Store is net positive by ₹2.2K because of adjustment gains of ₹8.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.5K and RTO loss ₹417.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and L hold ₹1.6K, 55% of aisle-level loss.
-* Clear FCC bin of ₹5.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹8.1K against GRN and STO inward before month close.</t>
+* Aisles D and L hold ₹1.6K, 55% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Yallapa Garden</t>
@@ -2870,9 +2435,7 @@
     <t xml:space="preserve">* Store is net positive by ₹2.3K because of adjustment gains of ₹8.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.6K, RTO loss ₹23 and Shortpick ₹7.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and H hold ₹8.1K, 57% of aisle-level loss.
-* Clear FCC bin of ₹6.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹8.9K against GRN and STO inward before month close.</t>
+* Aisles C and H hold ₹8.1K, 57% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Banashankari Network</t>
@@ -2881,10 +2444,7 @@
     <t xml:space="preserve">* Store is net positive by ₹2.4K because of adjustment gains of ₹20.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹8.9K, Shortpick ₹8.5K, RTO loss ₹370 and Other bins ₹128.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and E hold ₹12.5K, 77% of aisle-level loss.
-* Clear FCC bin of ₹8.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹8.5K shortpick value.
-* Validate adjustment gains of ₹20.3K against GRN and STO inward before month close.</t>
+* Aisles F and E hold ₹12.5K, 77% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR- Brookefield SS</t>
@@ -2893,10 +2453,7 @@
     <t xml:space="preserve">* Store is net positive by ₹2.4K because of adjustment gains of ₹19.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹15.3K, RTO loss ₹1.4K and Shortpick ₹490.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles K and I hold ₹4.2K, 53% of aisle-level loss.
-* Clear FCC bin of ₹15.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.4K with LM.
-* Validate adjustment gains of ₹19.6K against GRN and STO inward before month close.</t>
+* Aisles K and I hold ₹4.2K, 53% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Eldorado</t>
@@ -2904,8 +2461,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹2.7K because of adjustment gains of ₹2.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹138 and FCC bin ₹52.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹2.9K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Ramamurthy Nagar Network</t>
@@ -2913,9 +2469,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹2.7K because of adjustment gains of ₹5.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.4K and RTO loss ₹45.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹2.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹5.2K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Nagdevanahalli</t>
@@ -2924,9 +2478,7 @@
     <t xml:space="preserve">* Store is net positive by ₹2.8K because of adjustment gains of ₹8.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.5K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles M and F hold ₹3.5K, 66% of aisle-level loss.
-* Clear FCC bin of ₹5.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹8.3K against GRN and STO inward before month close.</t>
+* Aisles M and F hold ₹3.5K, 66% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Yelahanka Network</t>
@@ -2935,8 +2487,7 @@
     <t xml:space="preserve">* Store is net positive by ₹3.0K because of adjustment gains of ₹3.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹127 and FCC bin ₹39.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and A hold ₹5.7K, 92% of aisle-level loss.
-* Validate adjustment gains of ₹3.1K against GRN and STO inward before month close.</t>
+* Aisles H and A hold ₹5.7K, 92% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Thrippunithura</t>
@@ -2945,8 +2496,7 @@
     <t xml:space="preserve">* Store is net positive by ₹3.0K because of adjustment gains of ₹3.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹216 and RTO loss ₹86.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and K hold ₹1.6K, 65% of aisle-level loss.
-* Validate adjustment gains of ₹3.3K against GRN and STO inward before month close.</t>
+* Aisles H and K hold ₹1.6K, 65% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Basavanapura Network</t>
@@ -2955,9 +2505,7 @@
     <t xml:space="preserve">* Store is net positive by ₹3.3K because of adjustment gains of ₹8.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.2K, RTO loss ₹352 and Shortpick ₹253.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and A hold ₹7.5K, 55% of aisle-level loss.
-* Clear FCC bin of ₹4.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹8.1K against GRN and STO inward before month close.</t>
+* Aisles I and A hold ₹7.5K, 55% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-CV Raman Nagar SS</t>
@@ -2965,10 +2513,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹3.5K because of adjustment gains of ₹8.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: PO cancel ₹3.9K, FCC bin ₹787 and RTO loss ₹754.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹787 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹754 with LM and PO cancel ₹3.9K with procurement and DH.
-* Validate adjustment gains of ₹8.9K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Vallathol Padi</t>
@@ -2977,11 +2522,7 @@
     <t xml:space="preserve">* Store is net positive by ₹3.6K because of adjustment gains of ₹10.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.2K, Other bins ₹1.6K, RTO loss ₹925 and Shortpick ₹258.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and L hold ₹3.8K, 60% of aisle-level loss.
-* Clear FCC bin of ₹4.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹925 with LM.
-* Close out Other bins stock of ₹1.6K and post it back to inventory.
-* Validate adjustment gains of ₹10.6K against GRN and STO inward before month close.</t>
+* Aisles C and L hold ₹3.8K, 60% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Nagavara</t>
@@ -2990,9 +2531,7 @@
     <t xml:space="preserve">* Store is net positive by ₹3.9K because of adjustment gains of ₹10.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.4K and RTO loss ₹111.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and A hold ₹11.3K, 63% of aisle-level loss.
-* Clear FCC bin of ₹6.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹10.4K against GRN and STO inward before month close.</t>
+* Aisles D and A hold ₹11.3K, 63% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">Palakkad</t>
@@ -3003,8 +2542,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹4.1K because of adjustment gains of ₹4.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹275.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹4.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Rajarajeshwari Nagar</t>
@@ -3013,17 +2551,14 @@
     <t xml:space="preserve">* Store is net positive by ₹4.2K because of adjustment gains of ₹5.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.6K and RTO loss ₹167.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles K and J hold ₹3.6K, 65% of aisle-level loss.
-* Clear FCC bin of ₹1.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹5.9K against GRN and STO inward before month close.</t>
+* Aisles K and J hold ₹3.6K, 65% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Mahadevpura</t>
   </si>
   <si>
     <t xml:space="preserve">* Store is net positive by ₹4.4K because of adjustment gains of ₹4.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹4.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bannerghatta Network</t>
@@ -3032,10 +2567,7 @@
     <t xml:space="preserve">* Store is net positive by ₹4.7K because of adjustment gains of ₹11.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.3K, RTO loss ₹1.0K, Shortpick ₹176 and PO cancel ₹66.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and H hold ₹7.7K, 65% of aisle-level loss.
-* Clear FCC bin of ₹5.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.0K with LM.
-* Validate adjustment gains of ₹11.2K against GRN and STO inward before month close.</t>
+* Aisles G and H hold ₹7.7K, 65% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Soukya</t>
@@ -3044,8 +2576,7 @@
     <t xml:space="preserve">* Store is net positive by ₹4.8K because of adjustment gains of ₹5.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: PO cancel ₹194 and RTO loss ₹43.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles J and D hold ₹5.0K, 87% of aisle-level loss.
-* Validate adjustment gains of ₹5.1K against GRN and STO inward before month close.</t>
+* Aisles J and D hold ₹5.0K, 87% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Vani villas</t>
@@ -3054,8 +2585,7 @@
     <t xml:space="preserve">* Store is net positive by ₹4.9K because of adjustment gains of ₹5.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹59 and PO cancel ₹19.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and H hold ₹1.9K, 55% of aisle-level loss.
-* Validate adjustment gains of ₹5.0K against GRN and STO inward before month close.</t>
+* Aisles B and H hold ₹1.9K, 55% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kalyan Nagar Network</t>
@@ -3064,11 +2594,7 @@
     <t xml:space="preserve">* Store is net positive by ₹4.9K because of adjustment gains of ₹14.7K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹7.7K, Shortpick ₹780, RTO loss ₹736 and Other bins ₹535.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and C hold ₹9.1K, 79% of aisle-level loss.
-* Clear FCC bin of ₹7.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹736 with LM.
-* Close out Other bins stock of ₹535 and post it back to inventory.
-* Validate adjustment gains of ₹14.7K against GRN and STO inward before month close.</t>
+* Aisles I and C hold ₹9.1K, 79% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Peelamedu</t>
@@ -3076,10 +2602,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹5.0K because of adjustment gains of ₹13.8K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹8.0K and RTO loss ₹836.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹8.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹836 with LM.
-* Validate adjustment gains of ₹13.8K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kumaraswamy Layout</t>
@@ -3088,10 +2611,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.0K because of adjustment gains of ₹15.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹7.0K, RTO loss ₹3.3K and Shortpick ₹49.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles L and G hold ₹7.8K, 62% of aisle-level loss.
-* Clear FCC bin of ₹7.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹3.3K with LM.
-* Validate adjustment gains of ₹15.4K against GRN and STO inward before month close.</t>
+* Aisles L and G hold ₹7.8K, 62% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Kaloor</t>
@@ -3100,10 +2620,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.0K because of adjustment gains of ₹12.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.9K, Other bins ₹2.3K and RTO loss ₹139.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and N hold ₹2.0K, 61% of aisle-level loss.
-* Clear FCC bin of ₹4.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Close out Other bins stock of ₹2.3K and post it back to inventory.
-* Validate adjustment gains of ₹12.4K against GRN and STO inward before month close.</t>
+* Aisles A and N hold ₹2.0K, 61% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-KALYAN NAGAR NEW</t>
@@ -3112,9 +2629,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.1K because of adjustment gains of ₹20.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹14.6K, RTO loss ₹256, STO short receipt ₹251 and Shortpick ₹34.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles E and H hold ₹4.2K, 56% of aisle-level loss.
-* Clear FCC bin of ₹14.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹20.2K against GRN and STO inward before month close.</t>
+* Aisles E and H hold ₹4.2K, 56% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-SINGASANDRA NEW</t>
@@ -3123,9 +2638,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.1K because of adjustment gains of ₹10.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.3K, Shortpick ₹702 and RTO loss ₹119.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and E hold ₹6.3K, 76% of aisle-level loss.
-* Clear FCC bin of ₹4.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹10.3K against GRN and STO inward before month close.</t>
+* Aisles F and E hold ₹6.3K, 76% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Magadi Road</t>
@@ -3134,9 +2647,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.3K because of adjustment gains of ₹7.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.7K, RTO loss ₹403 and Other bins ₹115.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and N hold ₹3.5K, 53% of aisle-level loss.
-* Clear FCC bin of ₹1.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹7.6K against GRN and STO inward before month close.</t>
+* Aisles A and N hold ₹3.5K, 53% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Electronic City Network-2</t>
@@ -3145,18 +2656,14 @@
     <t xml:space="preserve">* Store is net positive by ₹5.4K because of adjustment gains of ₹19.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹10.7K, RTO loss ₹2.8K and Shortpick ₹400.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and A hold ₹19.6K, 79% of aisle-level loss.
-* Clear FCC bin of ₹10.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹2.8K with LM.
-* Validate adjustment gains of ₹19.3K against GRN and STO inward before month close.</t>
+* Aisles C and A hold ₹19.6K, 79% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">PAL-Kalpathy</t>
   </si>
   <si>
     <t xml:space="preserve">* Store is net positive by ₹5.5K because of adjustment gains of ₹5.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹5.5K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">HBL-Saptapur</t>
@@ -3165,8 +2672,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.6K because of adjustment gains of ₹5.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹8.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and E hold ₹3.3K, 76% of aisle-level loss.
-* Validate adjustment gains of ₹5.6K against GRN and STO inward before month close.</t>
+* Aisles D and E hold ₹3.3K, 76% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Margosa road</t>
@@ -3175,10 +2681,7 @@
     <t xml:space="preserve">* Store is net positive by ₹5.6K because of adjustment gains of ₹11.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.2K, RTO loss ₹686, PO cancel ₹348 and Shortpick ₹197.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and G hold ₹1.6K, 56% of aisle-level loss.
-* Clear FCC bin of ₹4.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹686 with LM.
-* Validate adjustment gains of ₹11.0K against GRN and STO inward before month close.</t>
+* Aisles F and G hold ₹1.6K, 56% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-YESHWANTPUR</t>
@@ -3187,9 +2690,7 @@
     <t xml:space="preserve">* Store is net positive by ₹6.1K because of adjustment gains of ₹10.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.9K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and E hold ₹10.0K, 62% of aisle-level loss.
-* Clear FCC bin of ₹3.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹10.0K against GRN and STO inward before month close.</t>
+* Aisles C and E hold ₹10.0K, 62% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR- Sonnenahalli New</t>
@@ -3198,9 +2699,7 @@
     <t xml:space="preserve">* Store is net positive by ₹6.2K because of adjustment gains of ₹7.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹933 and STO short receipt ₹61.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and A hold ₹4.7K, 85% of aisle-level loss.
-* Clear FCC bin of ₹933 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹7.1K against GRN and STO inward before month close.</t>
+* Aisles B and A hold ₹4.7K, 85% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bidaraguppe</t>
@@ -3208,16 +2707,14 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹6.3K because of adjustment gains of ₹6.7K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹356 and RTO loss ₹64.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹6.7K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Nehru Nagar</t>
   </si>
   <si>
     <t xml:space="preserve">* Store is net positive by ₹6.4K because of adjustment gains of ₹6.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹6.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-JP Nagar Network</t>
@@ -3226,9 +2723,7 @@
     <t xml:space="preserve">* Store is net positive by ₹6.4K because of adjustment gains of ₹11.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.1K, STO short receipt ₹491 and RTO loss ₹182.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and H hold ₹4.8K, 80% of aisle-level loss.
-* Clear FCC bin of ₹4.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹11.2K against GRN and STO inward before month close.</t>
+* Aisles F and H hold ₹4.8K, 80% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Rajendra Nagar</t>
@@ -3237,8 +2732,7 @@
     <t xml:space="preserve">* Store is net positive by ₹6.4K because of adjustment gains of ₹8.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Shortpick ₹781, FCC bin ₹392 and RTO loss ₹380.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and H hold ₹3.2K, 62% of aisle-level loss.
-* Validate adjustment gains of ₹8.0K against GRN and STO inward before month close.</t>
+* Aisles G and H hold ₹3.2K, 62% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Belathur</t>
@@ -3247,19 +2741,14 @@
     <t xml:space="preserve">* Store is net positive by ₹6.6K because of adjustment gains of ₹10.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Other bins ₹1.2K, FCC bin ₹815, Shortpick ₹635 and STO short receipt ₹593.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and F hold ₹8.7K, 95% of aisle-level loss.
-* Clear FCC bin of ₹815 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile STO short receipt ₹593 with MH and DH.
-* Close out Other bins stock of ₹1.2K and post it back to inventory.
-* Validate adjustment gains of ₹10.1K against GRN and STO inward before month close.</t>
+* Aisles D and F hold ₹8.7K, 95% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">PAL-TKV Nagar</t>
   </si>
   <si>
     <t xml:space="preserve">* Store is net positive by ₹6.6K because of adjustment gains of ₹6.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹6.6K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kannika Nagar</t>
@@ -3268,9 +2757,7 @@
     <t xml:space="preserve">* Store is net positive by ₹6.7K because of adjustment gains of ₹12.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.7K and Shortpick ₹30.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and H hold ₹7.3K, 62% of aisle-level loss.
-* Clear FCC bin of ₹5.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹12.5K against GRN and STO inward before month close.</t>
+* Aisles B and H hold ₹7.3K, 62% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-TC Palaya</t>
@@ -3278,9 +2765,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹6.8K because of adjustment gains of ₹11.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.8K, Shortpick ₹260 and RTO loss ₹73.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹3.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹11.0K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Junnasandra</t>
@@ -3288,8 +2773,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹6.8K because of adjustment gains of ₹7.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹333 and FCC bin ₹190.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹7.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Race Course</t>
@@ -3298,8 +2782,7 @@
     <t xml:space="preserve">* Store is net positive by ₹7.2K because of adjustment gains of ₹7.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹299.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and Q hold ₹3.9K, 59% of aisle-level loss.
-* Validate adjustment gains of ₹7.5K against GRN and STO inward before month close.</t>
+* Aisles H and Q hold ₹3.9K, 59% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Malleshwaram new</t>
@@ -3308,10 +2791,7 @@
     <t xml:space="preserve">* Store is net positive by ₹7.6K because of adjustment gains of ₹23.7K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹14.9K, RTO loss ₹878 and Shortpick ₹322.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and I hold ₹19.4K, 78% of aisle-level loss.
-* Clear FCC bin of ₹14.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹878 with LM.
-* Validate adjustment gains of ₹23.7K against GRN and STO inward before month close.</t>
+* Aisles H and I hold ₹19.4K, 78% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kadarenahalli SS</t>
@@ -3319,9 +2799,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹7.6K because of adjustment gains of ₹10.8K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.1K.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹3.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹10.8K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kadugodi</t>
@@ -3330,9 +2808,7 @@
     <t xml:space="preserve">* Store is net positive by ₹7.7K because of adjustment gains of ₹9.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.0K, Other bins ₹336, RTO loss ₹56 and Shortpick ₹27.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles N and F hold ₹9.1K, 71% of aisle-level loss.
-* Clear FCC bin of ₹1.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹9.1K against GRN and STO inward before month close.</t>
+* Aisles N and F hold ₹9.1K, 71% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RAGHAVENDRA LAYOUT NETWORK 2</t>
@@ -3341,9 +2817,7 @@
     <t xml:space="preserve">* Store is net positive by ₹7.8K because of adjustment gains of ₹12.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.5K and Shortpick ₹648.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and G hold ₹3.1K, 54% of aisle-level loss.
-* Clear FCC bin of ₹4.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹12.9K against GRN and STO inward before month close.</t>
+* Aisles C and G hold ₹3.1K, 54% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Kakkanad</t>
@@ -3352,11 +2826,7 @@
     <t xml:space="preserve">* Store is net positive by ₹8.0K because of adjustment gains of ₹19.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.7K, STO short receipt ₹3.8K and Other bins ₹1.0K.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and Q hold ₹2.8K, 61% of aisle-level loss.
-* Clear FCC bin of ₹6.7K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile STO short receipt ₹3.8K with MH and DH.
-* Close out Other bins stock of ₹1.0K and post it back to inventory.
-* Validate adjustment gains of ₹19.5K against GRN and STO inward before month close.</t>
+* Aisles G and Q hold ₹2.8K, 61% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Chickpet New</t>
@@ -3365,10 +2835,7 @@
     <t xml:space="preserve">* Store is net positive by ₹8.1K because of adjustment gains of ₹23.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹12.8K, STO short receipt ₹1.1K, Shortpick ₹842 and RTO loss ₹622.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles O and P hold ₹15.2K, 74% of aisle-level loss.
-* Clear FCC bin of ₹12.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹622 with LM and STO short receipt ₹1.1K with MH and DH.
-* Validate adjustment gains of ₹23.5K against GRN and STO inward before month close.</t>
+* Aisles O and P hold ₹15.2K, 74% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Aluva</t>
@@ -3377,9 +2844,7 @@
     <t xml:space="preserve">* Store is net positive by ₹8.6K because of adjustment gains of ₹10.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.1K and RTO loss ₹443.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and O hold ₹2.4K, 75% of aisle-level loss.
-* Clear FCC bin of ₹1.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹10.1K against GRN and STO inward before month close.</t>
+* Aisles F and O hold ₹2.4K, 75% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">HBL-Gokul Road</t>
@@ -3388,11 +2853,7 @@
     <t xml:space="preserve">* Store is net positive by ₹8.6K because of adjustment gains of ₹15.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.9K, Other bins ₹641 and RTO loss ₹555.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles N and D hold ₹1.2K, 51% of aisle-level loss.
-* Clear FCC bin of ₹5.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹555 with LM.
-* Close out Other bins stock of ₹641 and post it back to inventory.
-* Validate adjustment gains of ₹15.6K against GRN and STO inward before month close.</t>
+* Aisles N and D hold ₹1.2K, 51% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-TMC Layout</t>
@@ -3401,9 +2862,7 @@
     <t xml:space="preserve">* Store is net positive by ₹8.9K because of adjustment gains of ₹12.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.8K and RTO loss ₹346.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and A hold ₹2.1K, 73% of aisle-level loss.
-* Clear FCC bin of ₹2.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹12.0K against GRN and STO inward before month close.</t>
+* Aisles B and A hold ₹2.1K, 73% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-CV Raman Nagar Network</t>
@@ -3411,9 +2870,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹9.2K because of adjustment gains of ₹19.4K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹9.5K, RTO loss ₹471, Other bins ₹179 and Shortpick ₹43.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹9.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹19.4K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Ramnathapuram</t>
@@ -3422,9 +2879,7 @@
     <t xml:space="preserve">* Store is net positive by ₹9.3K because of adjustment gains of ₹11.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.4K and RTO loss ₹246.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles C and M hold ₹7.3K, 53% of aisle-level loss.
-* Clear FCC bin of ₹2.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹11.9K against GRN and STO inward before month close.</t>
+* Aisles C and M hold ₹7.3K, 53% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-HSR-Flower-Shop-1</t>
@@ -3432,9 +2887,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹9.4K because of adjustment gains of ₹10.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹953.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Reconcile RTO ₹953 with LM.
-* Validate adjustment gains of ₹10.3K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">KOC-Friendship nagar</t>
@@ -3443,19 +2896,14 @@
     <t xml:space="preserve">* Store is net positive by ₹10.2K because of adjustment gains of ₹17.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.4K, Other bins ₹624, RTO loss ₹509 and Shortpick ₹74.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles G and H hold ₹9.4K, 78% of aisle-level loss.
-* Clear FCC bin of ₹6.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹509 with LM.
-* Close out Other bins stock of ₹624 and post it back to inventory.
-* Validate adjustment gains of ₹17.9K against GRN and STO inward before month close.</t>
+* Aisles G and H hold ₹9.4K, 78% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-JP Nagar SS</t>
   </si>
   <si>
     <t xml:space="preserve">* Store is net positive by ₹11.0K because of adjustment gains of ₹11.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹11.0K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Abbigere</t>
@@ -3464,8 +2912,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.1K because of adjustment gains of ₹11.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹48.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and 1 hold ₹2.2K, 73% of aisle-level loss.
-* Validate adjustment gains of ₹11.1K against GRN and STO inward before month close.</t>
+* Aisles H and 1 hold ₹2.2K, 73% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-GUNJUR Network</t>
@@ -3473,10 +2920,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹11.1K because of adjustment gains of ₹14.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: STO short receipt ₹1.4K, FCC bin ₹1.0K, PO cancel ₹506 and RTO loss ₹62.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹1.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile STO short receipt ₹1.4K with MH and DH and PO cancel ₹506 with procurement and DH.
-* Validate adjustment gains of ₹14.1K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-New Gurappanya Palya</t>
@@ -3485,9 +2929,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.3K because of adjustment gains of ₹13.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.4K, Shortpick ₹232, RTO loss ₹107 and STO short receipt ₹54.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and G hold ₹6.9K, 87% of aisle-level loss.
-* Clear FCC bin of ₹1.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹13.1K against GRN and STO inward before month close.</t>
+* Aisles H and G hold ₹6.9K, 87% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Silicon Town</t>
@@ -3496,9 +2938,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.3K because of adjustment gains of ₹25.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹13.6K and RTO loss ₹258.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles J and I hold ₹1.5K, 55% of aisle-level loss.
-* Clear FCC bin of ₹13.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹25.2K against GRN and STO inward before month close.</t>
+* Aisles J and I hold ₹1.5K, 55% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Varthur</t>
@@ -3507,10 +2947,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.3K because of adjustment gains of ₹18.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.9K and RTO loss ₹863.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles N and B hold ₹7.0K, 60% of aisle-level loss.
-* Clear FCC bin of ₹5.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹863 with LM.
-* Validate adjustment gains of ₹18.1K against GRN and STO inward before month close.</t>
+* Aisles N and B hold ₹7.0K, 60% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Peenya SS</t>
@@ -3519,10 +2956,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.4K because of adjustment gains of ₹13.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹966 and FCC bin ₹756.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and O hold ₹6.3K, 56% of aisle-level loss.
-* Clear FCC bin of ₹756 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹966 with LM.
-* Validate adjustment gains of ₹13.1K against GRN and STO inward before month close.</t>
+* Aisles F and O hold ₹6.3K, 56% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Bannerghatta Network 2</t>
@@ -3531,10 +2965,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.6K because of adjustment gains of ₹15.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.0K, RTO loss ₹1.1K, STO short receipt ₹323 and Shortpick ₹262.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and G hold ₹10.1K, 88% of aisle-level loss.
-* Clear FCC bin of ₹2.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.1K with LM.
-* Validate adjustment gains of ₹15.3K against GRN and STO inward before month close.</t>
+* Aisles H and G hold ₹10.1K, 88% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Iggalur</t>
@@ -3543,9 +2974,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.6K because of adjustment gains of ₹12.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹627 and RTO loss ₹36.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles J and F hold ₹1.9K, 94% of aisle-level loss.
-* Clear FCC bin of ₹627 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹12.3K against GRN and STO inward before month close.</t>
+* Aisles J and F hold ₹1.9K, 94% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Vijayanagar</t>
@@ -3554,10 +2983,7 @@
     <t xml:space="preserve">* Store is net positive by ₹11.8K because of adjustment gains of ₹13.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹573, FCC bin ₹551 and PO cancel ₹19.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and B hold ₹3.1K, 62% of aisle-level loss.
-* Clear FCC bin of ₹551 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹573 with LM.
-* Validate adjustment gains of ₹13.0K against GRN and STO inward before month close.</t>
+* Aisles F and B hold ₹3.1K, 62% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Vijay Nagar SS</t>
@@ -3566,10 +2992,7 @@
     <t xml:space="preserve">* Store is net positive by ₹12.1K because of adjustment gains of ₹14.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.9K and RTO loss ₹534.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles P15 and Q hold ₹1.7K, 60% of aisle-level loss.
-* Clear FCC bin of ₹1.9K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹534 with LM.
-* Validate adjustment gains of ₹14.6K against GRN and STO inward before month close.</t>
+* Aisles P15 and Q hold ₹1.7K, 60% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Mico Layout Network</t>
@@ -3578,9 +3001,7 @@
     <t xml:space="preserve">* Store is net positive by ₹12.5K because of adjustment gains of ₹18.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.3K and RTO loss ₹146.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and G hold ₹2.9K, 56% of aisle-level loss.
-* Clear FCC bin of ₹6.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹18.9K against GRN and STO inward before month close.</t>
+* Aisles A and G hold ₹2.9K, 56% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Malagala</t>
@@ -3588,8 +3009,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹13.2K because of adjustment gains of ₹13.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Shortpick ₹63 and RTO loss ₹23.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹13.3K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Chikkajala</t>
@@ -3597,8 +3017,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹13.3K because of adjustment gains of ₹13.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹154 and RTO loss ₹51.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Validate adjustment gains of ₹13.5K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Kambipura</t>
@@ -3607,9 +3026,7 @@
     <t xml:space="preserve">* Store is net positive by ₹13.8K because of adjustment gains of ₹16.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.1K, Shortpick ₹124 and RTO loss ₹27.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and B hold ₹1.9K, 80% of aisle-level loss.
-* Clear FCC bin of ₹2.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹16.1K against GRN and STO inward before month close.</t>
+* Aisles D and B hold ₹1.9K, 80% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-JP Nagar Network-2</t>
@@ -3617,9 +3034,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹15.3K because of adjustment gains of ₹49.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Shortpick ₹34.0K.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Cycle count the shortpick bins against the ₹34.0K shortpick value.
-* Validate adjustment gains of ₹49.3K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">MYQ-Chamrajpura</t>
@@ -3628,8 +3043,7 @@
     <t xml:space="preserve">* Store is net positive by ₹15.5K because of adjustment gains of ₹15.7K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹91 and RTO loss ₹63.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles L and I hold ₹5.4K, 87% of aisle-level loss.
-* Validate adjustment gains of ₹15.7K against GRN and STO inward before month close.</t>
+* Aisles L and I hold ₹5.4K, 87% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Whitefield New</t>
@@ -3638,10 +3052,7 @@
     <t xml:space="preserve">* Store is net positive by ₹16.2K because of adjustment gains of ₹23.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.3K, RTO loss ₹692 and Shortpick ₹143.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles UU and I hold ₹6.0K, 71% of aisle-level loss.
-* Clear FCC bin of ₹6.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹692 with LM.
-* Validate adjustment gains of ₹23.3K against GRN and STO inward before month close.</t>
+* Aisles UU and I hold ₹6.0K, 71% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BTM-2 New</t>
@@ -3650,11 +3061,7 @@
     <t xml:space="preserve">* Store is net positive by ₹16.6K because of adjustment gains of ₹22.6K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.3K, Other bins ₹1.8K, RTO loss ₹680 and Shortpick ₹123.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles B and L hold ₹1.7K, 73% of aisle-level loss.
-* Clear FCC bin of ₹3.3K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹680 with LM.
-* Close out Other bins stock of ₹1.8K and post it back to inventory.
-* Validate adjustment gains of ₹22.6K against GRN and STO inward before month close.</t>
+* Aisles B and L hold ₹1.7K, 73% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-BEML Layout</t>
@@ -3662,9 +3069,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹16.7K because of adjustment gains of ₹19.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.0K, RTO loss ₹129 and Shortpick ₹18.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹3.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹19.9K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Sunrise Layout</t>
@@ -3673,9 +3078,7 @@
     <t xml:space="preserve">* Store is net positive by ₹18.3K because of adjustment gains of ₹22.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹3.8K and RTO loss ₹231.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and 1 hold ₹6.9K, 94% of aisle-level loss.
-* Clear FCC bin of ₹3.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹22.3K against GRN and STO inward before month close.</t>
+* Aisles I and 1 hold ₹6.9K, 94% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-27th Main Road</t>
@@ -3684,10 +3087,7 @@
     <t xml:space="preserve">* Store is net positive by ₹19.4K because of adjustment gains of ₹22.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.4K and RTO loss ₹697.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and E hold ₹5.7K, 82% of aisle-level loss.
-* Clear FCC bin of ₹2.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹697 with LM.
-* Validate adjustment gains of ₹22.5K against GRN and STO inward before month close.</t>
+* Aisles A and E hold ₹5.7K, 82% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Goraguntepalya</t>
@@ -3695,9 +3095,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹21.3K because of adjustment gains of ₹22.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Other bins ₹854, RTO loss ₹51 and FCC bin ₹19.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Close out Other bins stock of ₹854 and post it back to inventory.
-* Validate adjustment gains of ₹22.3K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Singasandra Network</t>
@@ -3706,9 +3104,7 @@
     <t xml:space="preserve">* Store is net positive by ₹22.6K because of adjustment gains of ₹25.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.5K and RTO loss ₹113.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and H hold ₹6.8K, 100% of aisle-level loss.
-* Clear FCC bin of ₹2.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹25.2K against GRN and STO inward before month close.</t>
+* Aisles I and H hold ₹6.8K, 100% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Hadosiddapura</t>
@@ -3717,9 +3113,7 @@
     <t xml:space="preserve">* Store is net positive by ₹23.2K because of adjustment gains of ₹26.1K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹1.5K, Shortpick ₹527, Other bins ₹434 and STO short receipt ₹404.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and G hold ₹2.4K, 74% of aisle-level loss.
-* Clear FCC bin of ₹1.5K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹26.1K against GRN and STO inward before month close.</t>
+* Aisles I and G hold ₹2.4K, 74% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Mathikere New</t>
@@ -3728,9 +3122,7 @@
     <t xml:space="preserve">* Store is net positive by ₹25.1K because of adjustment gains of ₹27.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: STO short receipt ₹2.3K and RTO loss ₹134.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and K hold ₹5.5K, 59% of aisle-level loss.
-* Reconcile STO short receipt ₹2.3K with MH and DH.
-* Validate adjustment gains of ₹27.5K against GRN and STO inward before month close.</t>
+* Aisles I and K hold ₹5.5K, 59% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Whitefield Network-2</t>
@@ -3739,10 +3131,7 @@
     <t xml:space="preserve">* Store is net positive by ₹25.8K because of adjustment gains of ₹35.3K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹5.0K, Shortpick ₹4.4K and RTO loss ₹203.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles A and S hold ₹3.7K, 82% of aisle-level loss.
-* Clear FCC bin of ₹5.0K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Cycle count the shortpick bins against the ₹4.4K shortpick value.
-* Validate adjustment gains of ₹35.3K against GRN and STO inward before month close.</t>
+* Aisles A and S hold ₹3.7K, 82% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">COI-Singanallur</t>
@@ -3751,8 +3140,7 @@
     <t xml:space="preserve">* Store is net positive by ₹28.5K because of adjustment gains of ₹29.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹468.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles H and G hold ₹5.6K, 80% of aisle-level loss.
-* Validate adjustment gains of ₹29.0K against GRN and STO inward before month close.</t>
+* Aisles H and G hold ₹5.6K, 80% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR - Bhadrappa Layout</t>
@@ -3761,9 +3149,7 @@
     <t xml:space="preserve">* Store is net positive by ₹30.9K because of adjustment gains of ₹31.9K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹673, RTO loss ₹307 and Shortpick ₹73.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles S and 1 hold ₹2.6K, 100% of aisle-level loss.
-* Clear FCC bin of ₹673 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹31.9K against GRN and STO inward before month close.</t>
+* Aisles S and 1 hold ₹2.6K, 100% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Gunjur New</t>
@@ -3772,10 +3158,7 @@
     <t xml:space="preserve">* Store is net positive by ₹31.3K because of adjustment gains of ₹46.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹14.8K and RTO loss ₹516.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles D and G hold ₹10.3K, 62% of aisle-level loss.
-* Clear FCC bin of ₹14.8K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹516 with LM.
-* Validate adjustment gains of ₹46.5K against GRN and STO inward before month close.</t>
+* Aisles D and G hold ₹10.3K, 62% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Michael Palaya</t>
@@ -3784,10 +3167,7 @@
     <t xml:space="preserve">* Store is net positive by ₹34.7K because of adjustment gains of ₹38.2K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: RTO loss ₹1.3K, FCC bin ₹1.2K and Shortpick ₹970.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles F and B hold ₹3.7K, 100% of aisle-level loss.
-* Clear FCC bin of ₹1.2K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.3K with LM.
-* Validate adjustment gains of ₹38.2K against GRN and STO inward before month close.</t>
+* Aisles F and B hold ₹3.7K, 100% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Agrahara Road</t>
@@ -3796,9 +3176,7 @@
     <t xml:space="preserve">* Store is net positive by ₹36.7K because of adjustment gains of ₹39.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹2.4K, Shortpick ₹195 and RTO loss ₹152.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and 1 hold ₹3.0K, 83% of aisle-level loss.
-* Clear FCC bin of ₹2.4K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹39.5K against GRN and STO inward before month close.</t>
+* Aisles I and 1 hold ₹3.0K, 83% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Aswath Nagar</t>
@@ -3806,11 +3184,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹37.4K because of adjustment gains of ₹46.5K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹6.6K, Other bins ₹1.2K and RTO loss ₹1.2K.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Clear FCC bin of ₹6.6K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.2K with LM.
-* Close out Other bins stock of ₹1.2K and post it back to inventory.
-* Validate adjustment gains of ₹46.5K against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-RAGHAVENDRA LAYOUT NETWORK</t>
@@ -3819,9 +3193,7 @@
     <t xml:space="preserve">* Store is net positive by ₹42.8K because of adjustment gains of ₹44.0K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹978, Shortpick ₹184 and RTO loss ₹73.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles I and G hold ₹11.0K, 94% of aisle-level loss.
-* Clear FCC bin of ₹978 by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Validate adjustment gains of ₹44.0K against GRN and STO inward before month close.</t>
+* Aisles I and G hold ₹11.0K, 94% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Choodasandra</t>
@@ -3830,11 +3202,7 @@
     <t xml:space="preserve">* Store is net positive by ₹44.4K because of adjustment gains of ₹51.7K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: FCC bin ₹4.1K, RTO loss ₹1.5K, Other bins ₹1.1K and Shortpick ₹672.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisles 1 and F hold ₹3.8K, 75% of aisle-level loss.
-* Clear FCC bin of ₹4.1K by tomorrow. Stock traced goes back to its bin and posts as adjustment gain.
-* Reconcile RTO ₹1.5K with LM.
-* Close out Other bins stock of ₹1.1K and post it back to inventory.
-* Validate adjustment gains of ₹51.7K against GRN and STO inward before month close.</t>
+* Aisles 1 and F hold ₹3.8K, 75% of aisle-level loss.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Attibele</t>
@@ -3843,9 +3211,7 @@
     <t xml:space="preserve">* Store is net positive by ₹45.2K because of adjustment gains of ₹46.8K. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: STO short receipt ₹1.2K, FCC bin ₹291 and RTO loss ₹179.
 * SKU-level data not shared for this store, so category and SKU view is not covered.
-* Aisle B holds all of the aisle-level loss at ₹18.7K.
-* Reconcile STO short receipt ₹1.2K with MH and DH.
-* Validate adjustment gains of ₹46.8K against GRN and STO inward before month close.</t>
+* Aisle B holds all of the aisle-level loss at ₹18.7K.</t>
   </si>
   <si>
     <t xml:space="preserve">BLR-Balagere SS</t>
@@ -3853,9 +3219,7 @@
   <si>
     <t xml:space="preserve">* Store is net positive by ₹91.5K because of adjustment gains of ₹2.53L. Gains to be checked for FCC stock traced vs GRN or STO inward misses.
 * Loss buckets still open: Shortpick ₹1.62L.
-* SKU-level data not shared for this store, so category and SKU view is not covered.
-* Cycle count the shortpick bins against the ₹1.62L shortpick value.
-* Validate adjustment gains of ₹2.53L against GRN and STO inward before month close.</t>
+* SKU-level data not shared for this store, so category and SKU view is not covered.</t>
   </si>
 </sst>
 </file>
@@ -8303,7 +7667,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="18" t="s">
         <v>270</v>
       </c>
@@ -8366,7 +7730,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="18" t="s">
         <v>270</v>
       </c>
@@ -8427,7 +7791,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="18" t="s">
         <v>270</v>
       </c>
@@ -8488,7 +7852,7 @@
       </c>
       <c r="T162" s="21"/>
     </row>
-    <row r="163" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="18" t="s">
         <v>270</v>
       </c>
@@ -8549,7 +7913,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="18" t="s">
         <v>270</v>
       </c>
@@ -8606,7 +7970,7 @@
       <c r="S164" s="21"/>
       <c r="T164" s="21"/>
     </row>
-    <row r="165" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="18" t="s">
         <v>270</v>
       </c>
@@ -8663,7 +8027,7 @@
       <c r="S165" s="21"/>
       <c r="T165" s="21"/>
     </row>
-    <row r="166" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="18" t="s">
         <v>270</v>
       </c>
@@ -8720,7 +8084,7 @@
       <c r="S166" s="21"/>
       <c r="T166" s="21"/>
     </row>
-    <row r="167" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="18" t="s">
         <v>270</v>
       </c>
@@ -8779,7 +8143,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="18" t="s">
         <v>270</v>
       </c>
@@ -8838,7 +8202,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="18" t="s">
         <v>270</v>
       </c>
@@ -8895,7 +8259,7 @@
       <c r="S169" s="21"/>
       <c r="T169" s="21"/>
     </row>
-    <row r="170" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="18" t="s">
         <v>270</v>
       </c>
@@ -8952,7 +8316,7 @@
       <c r="S170" s="21"/>
       <c r="T170" s="21"/>
     </row>
-    <row r="171" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="18" t="s">
         <v>270</v>
       </c>
@@ -9009,7 +8373,7 @@
       <c r="S171" s="21"/>
       <c r="T171" s="21"/>
     </row>
-    <row r="172" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="18" t="s">
         <v>270</v>
       </c>
@@ -9068,7 +8432,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="18" t="s">
         <v>270</v>
       </c>
@@ -9125,7 +8489,7 @@
       <c r="S173" s="21"/>
       <c r="T173" s="21"/>
     </row>
-    <row r="174" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="18" t="s">
         <v>270</v>
       </c>
@@ -9182,7 +8546,7 @@
       <c r="S174" s="21"/>
       <c r="T174" s="21"/>
     </row>
-    <row r="175" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="18" t="s">
         <v>270</v>
       </c>
@@ -9241,7 +8605,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="18"/>
       <c r="B176" s="18" t="s">
         <v>271</v>
@@ -9298,7 +8662,7 @@
       <c r="S176" s="21"/>
       <c r="T176" s="21"/>
     </row>
-    <row r="177" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="18" t="s">
         <v>270</v>
       </c>
@@ -9355,7 +8719,7 @@
       <c r="S177" s="21"/>
       <c r="T177" s="21"/>
     </row>
-    <row r="178" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="18" t="s">
         <v>270</v>
       </c>
@@ -9414,7 +8778,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="18" t="s">
         <v>270</v>
       </c>
@@ -9471,7 +8835,7 @@
       <c r="S179" s="21"/>
       <c r="T179" s="21"/>
     </row>
-    <row r="180" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="18" t="s">
         <v>270</v>
       </c>
@@ -9528,7 +8892,7 @@
       <c r="S180" s="21"/>
       <c r="T180" s="21"/>
     </row>
-    <row r="181" customFormat="false" ht="198" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="18" t="s">
         <v>270</v>
       </c>
@@ -9587,7 +8951,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="18" t="s">
         <v>270</v>
       </c>
@@ -9646,7 +9010,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="18" t="s">
         <v>270</v>
       </c>
@@ -9703,7 +9067,7 @@
       <c r="S183" s="21"/>
       <c r="T183" s="21"/>
     </row>
-    <row r="184" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="18" t="s">
         <v>270</v>
       </c>
@@ -9760,7 +9124,7 @@
       <c r="S184" s="21"/>
       <c r="T184" s="21"/>
     </row>
-    <row r="185" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="18" t="s">
         <v>270</v>
       </c>
@@ -9817,7 +9181,7 @@
       <c r="S185" s="21"/>
       <c r="T185" s="21"/>
     </row>
-    <row r="186" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="18" t="s">
         <v>270</v>
       </c>
@@ -9880,7 +9244,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="18" t="s">
         <v>270</v>
       </c>
@@ -9939,7 +9303,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="18" t="s">
         <v>270</v>
       </c>
@@ -9996,7 +9360,7 @@
       <c r="S188" s="21"/>
       <c r="T188" s="21"/>
     </row>
-    <row r="189" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="18" t="s">
         <v>270</v>
       </c>
@@ -10053,7 +9417,7 @@
       <c r="S189" s="21"/>
       <c r="T189" s="21"/>
     </row>
-    <row r="190" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="18" t="s">
         <v>270</v>
       </c>
@@ -10112,7 +9476,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="18" t="s">
         <v>270</v>
       </c>
@@ -10169,7 +9533,7 @@
       <c r="S191" s="21"/>
       <c r="T191" s="21"/>
     </row>
-    <row r="192" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="18" t="s">
         <v>270</v>
       </c>
@@ -10226,7 +9590,7 @@
       <c r="S192" s="21"/>
       <c r="T192" s="21"/>
     </row>
-    <row r="193" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="18" t="s">
         <v>270</v>
       </c>
@@ -10285,7 +9649,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="18" t="s">
         <v>270</v>
       </c>
@@ -10342,7 +9706,7 @@
       <c r="S194" s="21"/>
       <c r="T194" s="21"/>
     </row>
-    <row r="195" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="18" t="s">
         <v>270</v>
       </c>
@@ -10399,7 +9763,7 @@
       <c r="S195" s="21"/>
       <c r="T195" s="21"/>
     </row>
-    <row r="196" customFormat="false" ht="162" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="18" t="s">
         <v>270</v>
       </c>
@@ -10458,7 +9822,7 @@
         <v>38000</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="18" t="s">
         <v>270</v>
       </c>
@@ -10515,7 +9879,7 @@
       <c r="S197" s="21"/>
       <c r="T197" s="21"/>
     </row>
-    <row r="198" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="18" t="s">
         <v>270</v>
       </c>
@@ -10572,7 +9936,7 @@
       <c r="S198" s="21"/>
       <c r="T198" s="21"/>
     </row>
-    <row r="199" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="18" t="s">
         <v>270</v>
       </c>
@@ -10629,7 +9993,7 @@
       <c r="S199" s="21"/>
       <c r="T199" s="21"/>
     </row>
-    <row r="200" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="18" t="s">
         <v>270</v>
       </c>
@@ -10686,7 +10050,7 @@
       <c r="S200" s="21"/>
       <c r="T200" s="21"/>
     </row>
-    <row r="201" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="18" t="s">
         <v>270</v>
       </c>
@@ -10743,7 +10107,7 @@
       <c r="S201" s="21"/>
       <c r="T201" s="21"/>
     </row>
-    <row r="202" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="18" t="s">
         <v>270</v>
       </c>
@@ -10800,7 +10164,7 @@
       <c r="S202" s="21"/>
       <c r="T202" s="21"/>
     </row>
-    <row r="203" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="18" t="s">
         <v>270</v>
       </c>
@@ -10857,7 +10221,7 @@
       <c r="S203" s="21"/>
       <c r="T203" s="21"/>
     </row>
-    <row r="204" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="18" t="s">
         <v>270</v>
       </c>
@@ -10914,7 +10278,7 @@
       <c r="S204" s="21"/>
       <c r="T204" s="21"/>
     </row>
-    <row r="205" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="18" t="s">
         <v>270</v>
       </c>
@@ -10973,7 +10337,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="18" t="s">
         <v>270</v>
       </c>
@@ -11030,7 +10394,7 @@
       <c r="S206" s="21"/>
       <c r="T206" s="21"/>
     </row>
-    <row r="207" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="18" t="s">
         <v>270</v>
       </c>
@@ -11087,7 +10451,7 @@
       <c r="S207" s="21"/>
       <c r="T207" s="21"/>
     </row>
-    <row r="208" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="18" t="s">
         <v>270</v>
       </c>
@@ -11146,7 +10510,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="18" t="s">
         <v>270</v>
       </c>
@@ -11203,7 +10567,7 @@
       <c r="S209" s="21"/>
       <c r="T209" s="21"/>
     </row>
-    <row r="210" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="18" t="s">
         <v>270</v>
       </c>
@@ -11260,7 +10624,7 @@
       <c r="S210" s="21"/>
       <c r="T210" s="21"/>
     </row>
-    <row r="211" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="18" t="s">
         <v>270</v>
       </c>
@@ -11319,7 +10683,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="18" t="s">
         <v>270</v>
       </c>
@@ -11376,7 +10740,7 @@
       <c r="S212" s="21"/>
       <c r="T212" s="21"/>
     </row>
-    <row r="213" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="18" t="s">
         <v>270</v>
       </c>
@@ -11433,7 +10797,7 @@
       <c r="S213" s="21"/>
       <c r="T213" s="21"/>
     </row>
-    <row r="214" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="18" t="s">
         <v>270</v>
       </c>
@@ -11490,7 +10854,7 @@
       <c r="S214" s="21"/>
       <c r="T214" s="21"/>
     </row>
-    <row r="215" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="18" t="s">
         <v>270</v>
       </c>
@@ -11547,7 +10911,7 @@
       <c r="S215" s="21"/>
       <c r="T215" s="21"/>
     </row>
-    <row r="216" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="18" t="s">
         <v>270</v>
       </c>
@@ -11604,7 +10968,7 @@
       <c r="S216" s="21"/>
       <c r="T216" s="21"/>
     </row>
-    <row r="217" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="18" t="s">
         <v>270</v>
       </c>
@@ -11661,7 +11025,7 @@
       <c r="S217" s="21"/>
       <c r="T217" s="21"/>
     </row>
-    <row r="218" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="18" t="s">
         <v>270</v>
       </c>
@@ -11718,7 +11082,7 @@
       <c r="S218" s="21"/>
       <c r="T218" s="21"/>
     </row>
-    <row r="219" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="18" t="s">
         <v>270</v>
       </c>
@@ -11775,7 +11139,7 @@
       <c r="S219" s="21"/>
       <c r="T219" s="21"/>
     </row>
-    <row r="220" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="18" t="s">
         <v>270</v>
       </c>
@@ -11832,7 +11196,7 @@
       <c r="S220" s="21"/>
       <c r="T220" s="21"/>
     </row>
-    <row r="221" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="18" t="s">
         <v>270</v>
       </c>
@@ -11889,7 +11253,7 @@
       <c r="S221" s="21"/>
       <c r="T221" s="21"/>
     </row>
-    <row r="222" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="18" t="s">
         <v>270</v>
       </c>
@@ -11946,7 +11310,7 @@
       <c r="S222" s="21"/>
       <c r="T222" s="21"/>
     </row>
-    <row r="223" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="18" t="s">
         <v>270</v>
       </c>
@@ -12005,7 +11369,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="18" t="s">
         <v>270</v>
       </c>
@@ -12062,7 +11426,7 @@
       <c r="S224" s="21"/>
       <c r="T224" s="21"/>
     </row>
-    <row r="225" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="18" t="s">
         <v>270</v>
       </c>
@@ -12123,7 +11487,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="18" t="s">
         <v>270</v>
       </c>
@@ -12182,7 +11546,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="18" t="s">
         <v>270</v>
       </c>
@@ -12239,7 +11603,7 @@
       <c r="S227" s="21"/>
       <c r="T227" s="21"/>
     </row>
-    <row r="228" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="18" t="s">
         <v>270</v>
       </c>
@@ -12296,7 +11660,7 @@
       <c r="S228" s="21"/>
       <c r="T228" s="21"/>
     </row>
-    <row r="229" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="18" t="s">
         <v>270</v>
       </c>
@@ -12353,7 +11717,7 @@
       <c r="S229" s="21"/>
       <c r="T229" s="21"/>
     </row>
-    <row r="230" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="18" t="s">
         <v>270</v>
       </c>
@@ -12410,7 +11774,7 @@
       <c r="S230" s="21"/>
       <c r="T230" s="21"/>
     </row>
-    <row r="231" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="18" t="s">
         <v>270</v>
       </c>
@@ -12467,7 +11831,7 @@
       <c r="S231" s="21"/>
       <c r="T231" s="21"/>
     </row>
-    <row r="232" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="18" t="s">
         <v>270</v>
       </c>
@@ -12524,7 +11888,7 @@
       <c r="S232" s="21"/>
       <c r="T232" s="21"/>
     </row>
-    <row r="233" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="18" t="s">
         <v>270</v>
       </c>
@@ -12581,7 +11945,7 @@
       <c r="S233" s="21"/>
       <c r="T233" s="21"/>
     </row>
-    <row r="234" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="18" t="s">
         <v>270</v>
       </c>
@@ -12638,7 +12002,7 @@
       <c r="S234" s="21"/>
       <c r="T234" s="21"/>
     </row>
-    <row r="235" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="18" t="s">
         <v>270</v>
       </c>
@@ -12695,7 +12059,7 @@
       <c r="S235" s="21"/>
       <c r="T235" s="21"/>
     </row>
-    <row r="236" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="18" t="s">
         <v>270</v>
       </c>
@@ -12754,7 +12118,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="18" t="s">
         <v>270</v>
       </c>
@@ -12811,7 +12175,7 @@
       <c r="S237" s="21"/>
       <c r="T237" s="21"/>
     </row>
-    <row r="238" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="18" t="s">
         <v>270</v>
       </c>
@@ -12870,7 +12234,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="18" t="s">
         <v>270</v>
       </c>
@@ -12927,7 +12291,7 @@
       <c r="S239" s="21"/>
       <c r="T239" s="21"/>
     </row>
-    <row r="240" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="18" t="s">
         <v>270</v>
       </c>
@@ -12986,7 +12350,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="18" t="s">
         <v>270</v>
       </c>
@@ -13043,7 +12407,7 @@
       <c r="S241" s="21"/>
       <c r="T241" s="21"/>
     </row>
-    <row r="242" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="18" t="s">
         <v>270</v>
       </c>
@@ -13100,7 +12464,7 @@
       <c r="S242" s="21"/>
       <c r="T242" s="21"/>
     </row>
-    <row r="243" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="18" t="s">
         <v>270</v>
       </c>
@@ -13157,7 +12521,7 @@
       <c r="S243" s="21"/>
       <c r="T243" s="21"/>
     </row>
-    <row r="244" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="18" t="s">
         <v>270</v>
       </c>
@@ -13214,7 +12578,7 @@
       <c r="S244" s="21"/>
       <c r="T244" s="21"/>
     </row>
-    <row r="245" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="18" t="s">
         <v>270</v>
       </c>
@@ -13271,7 +12635,7 @@
       <c r="S245" s="21"/>
       <c r="T245" s="21"/>
     </row>
-    <row r="246" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="18" t="s">
         <v>270</v>
       </c>
@@ -13328,7 +12692,7 @@
       <c r="S246" s="21"/>
       <c r="T246" s="21"/>
     </row>
-    <row r="247" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="18" t="s">
         <v>270</v>
       </c>
@@ -13385,7 +12749,7 @@
       <c r="S247" s="21"/>
       <c r="T247" s="21"/>
     </row>
-    <row r="248" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="18" t="s">
         <v>270</v>
       </c>
@@ -13444,7 +12808,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="18" t="s">
         <v>270</v>
       </c>
@@ -13501,7 +12865,7 @@
       <c r="S249" s="21"/>
       <c r="T249" s="21"/>
     </row>
-    <row r="250" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="18" t="s">
         <v>270</v>
       </c>
@@ -13562,7 +12926,7 @@
       </c>
       <c r="T250" s="21"/>
     </row>
-    <row r="251" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="18" t="s">
         <v>270</v>
       </c>
@@ -13619,7 +12983,7 @@
       <c r="S251" s="21"/>
       <c r="T251" s="21"/>
     </row>
-    <row r="252" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="18" t="s">
         <v>270</v>
       </c>
@@ -13676,7 +13040,7 @@
       <c r="S252" s="21"/>
       <c r="T252" s="21"/>
     </row>
-    <row r="253" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="18" t="s">
         <v>270</v>
       </c>
@@ -13733,7 +13097,7 @@
       <c r="S253" s="21"/>
       <c r="T253" s="21"/>
     </row>
-    <row r="254" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="18" t="s">
         <v>270</v>
       </c>
@@ -13790,7 +13154,7 @@
       <c r="S254" s="21"/>
       <c r="T254" s="21"/>
     </row>
-    <row r="255" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="18" t="s">
         <v>270</v>
       </c>
@@ -13847,7 +13211,7 @@
       <c r="S255" s="21"/>
       <c r="T255" s="21"/>
     </row>
-    <row r="256" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="18" t="s">
         <v>270</v>
       </c>
@@ -13906,7 +13270,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="18" t="s">
         <v>270</v>
       </c>
@@ -13965,7 +13329,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="18" t="s">
         <v>270</v>
       </c>
@@ -14022,7 +13386,7 @@
       <c r="S258" s="21"/>
       <c r="T258" s="21"/>
     </row>
-    <row r="259" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="18" t="s">
         <v>270</v>
       </c>
@@ -14079,7 +13443,7 @@
       <c r="S259" s="21"/>
       <c r="T259" s="21"/>
     </row>
-    <row r="260" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="18" t="s">
         <v>270</v>
       </c>
@@ -14136,7 +13500,7 @@
       <c r="S260" s="21"/>
       <c r="T260" s="21"/>
     </row>
-    <row r="261" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="18" t="s">
         <v>270</v>
       </c>
@@ -14193,7 +13557,7 @@
       <c r="S261" s="21"/>
       <c r="T261" s="21"/>
     </row>
-    <row r="262" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="18" t="s">
         <v>270</v>
       </c>
@@ -14250,7 +13614,7 @@
       <c r="S262" s="21"/>
       <c r="T262" s="21"/>
     </row>
-    <row r="263" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="18" t="s">
         <v>270</v>
       </c>
@@ -14307,7 +13671,7 @@
       <c r="S263" s="21"/>
       <c r="T263" s="21"/>
     </row>
-    <row r="264" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="18" t="s">
         <v>270</v>
       </c>
@@ -14364,7 +13728,7 @@
       <c r="S264" s="21"/>
       <c r="T264" s="21"/>
     </row>
-    <row r="265" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="18" t="s">
         <v>270</v>
       </c>
@@ -14423,7 +13787,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="18" t="s">
         <v>270</v>
       </c>
@@ -14482,7 +13846,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="18" t="s">
         <v>270</v>
       </c>
@@ -14541,7 +13905,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="18" t="s">
         <v>270</v>
       </c>
@@ -14598,7 +13962,7 @@
       <c r="S268" s="21"/>
       <c r="T268" s="21"/>
     </row>
-    <row r="269" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="18" t="s">
         <v>270</v>
       </c>
@@ -14655,7 +14019,7 @@
       <c r="S269" s="21"/>
       <c r="T269" s="21"/>
     </row>
-    <row r="270" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="18" t="s">
         <v>270</v>
       </c>
@@ -14714,7 +14078,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="18" t="s">
         <v>270</v>
       </c>
@@ -14771,7 +14135,7 @@
       <c r="S271" s="21"/>
       <c r="T271" s="21"/>
     </row>
-    <row r="272" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="18" t="s">
         <v>270</v>
       </c>
@@ -14828,7 +14192,7 @@
       <c r="S272" s="21"/>
       <c r="T272" s="21"/>
     </row>
-    <row r="273" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="18" t="s">
         <v>270</v>
       </c>
@@ -14885,7 +14249,7 @@
       <c r="S273" s="21"/>
       <c r="T273" s="21"/>
     </row>
-    <row r="274" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="18" t="s">
         <v>270</v>
       </c>
@@ -14942,7 +14306,7 @@
       <c r="S274" s="21"/>
       <c r="T274" s="21"/>
     </row>
-    <row r="275" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="18" t="s">
         <v>270</v>
       </c>
@@ -14999,7 +14363,7 @@
       <c r="S275" s="21"/>
       <c r="T275" s="21"/>
     </row>
-    <row r="276" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="18" t="s">
         <v>270</v>
       </c>
@@ -15056,7 +14420,7 @@
       <c r="S276" s="21"/>
       <c r="T276" s="21"/>
     </row>
-    <row r="277" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="18" t="s">
         <v>270</v>
       </c>
@@ -15113,7 +14477,7 @@
       <c r="S277" s="21"/>
       <c r="T277" s="21"/>
     </row>
-    <row r="278" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="18" t="s">
         <v>270</v>
       </c>
@@ -15170,7 +14534,7 @@
       <c r="S278" s="21"/>
       <c r="T278" s="21"/>
     </row>
-    <row r="279" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="18" t="s">
         <v>270</v>
       </c>
@@ -15227,7 +14591,7 @@
       <c r="S279" s="21"/>
       <c r="T279" s="21"/>
     </row>
-    <row r="280" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="18" t="s">
         <v>270</v>
       </c>
@@ -15284,7 +14648,7 @@
       <c r="S280" s="21"/>
       <c r="T280" s="21"/>
     </row>
-    <row r="281" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="18" t="s">
         <v>270</v>
       </c>
@@ -15398,7 +14762,7 @@
       <c r="S282" s="21"/>
       <c r="T282" s="21"/>
     </row>
-    <row r="283" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="18" t="s">
         <v>270</v>
       </c>
@@ -15455,7 +14819,7 @@
       <c r="S283" s="21"/>
       <c r="T283" s="21"/>
     </row>
-    <row r="284" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="18" t="s">
         <v>270</v>
       </c>
@@ -15512,7 +14876,7 @@
       <c r="S284" s="21"/>
       <c r="T284" s="21"/>
     </row>
-    <row r="285" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="18" t="s">
         <v>270</v>
       </c>
@@ -15569,7 +14933,7 @@
       <c r="S285" s="21"/>
       <c r="T285" s="21"/>
     </row>
-    <row r="286" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="18" t="s">
         <v>270</v>
       </c>
@@ -15626,7 +14990,7 @@
       <c r="S286" s="21"/>
       <c r="T286" s="21"/>
     </row>
-    <row r="287" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="18" t="s">
         <v>270</v>
       </c>
@@ -15683,7 +15047,7 @@
       <c r="S287" s="21"/>
       <c r="T287" s="21"/>
     </row>
-    <row r="288" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="18" t="s">
         <v>270</v>
       </c>
@@ -15742,7 +15106,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="18" t="s">
         <v>270</v>
       </c>
@@ -15799,7 +15163,7 @@
       <c r="S289" s="21"/>
       <c r="T289" s="21"/>
     </row>
-    <row r="290" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="18" t="s">
         <v>270</v>
       </c>
@@ -15856,7 +15220,7 @@
       <c r="S290" s="21"/>
       <c r="T290" s="21"/>
     </row>
-    <row r="291" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="18" t="s">
         <v>270</v>
       </c>
@@ -15913,7 +15277,7 @@
       <c r="S291" s="21"/>
       <c r="T291" s="21"/>
     </row>
-    <row r="292" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="18" t="s">
         <v>270</v>
       </c>
@@ -15970,7 +15334,7 @@
       <c r="S292" s="21"/>
       <c r="T292" s="21"/>
     </row>
-    <row r="293" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="18" t="s">
         <v>270</v>
       </c>
@@ -16027,7 +15391,7 @@
       <c r="S293" s="21"/>
       <c r="T293" s="21"/>
     </row>
-    <row r="294" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="18" t="s">
         <v>270</v>
       </c>
@@ -16084,7 +15448,7 @@
       <c r="S294" s="21"/>
       <c r="T294" s="21"/>
     </row>
-    <row r="295" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="18" t="s">
         <v>270</v>
       </c>
@@ -16198,7 +15562,7 @@
       <c r="S296" s="21"/>
       <c r="T296" s="21"/>
     </row>
-    <row r="297" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="18" t="s">
         <v>270</v>
       </c>
@@ -16255,7 +15619,7 @@
       <c r="S297" s="21"/>
       <c r="T297" s="21"/>
     </row>
-    <row r="298" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="18" t="s">
         <v>270</v>
       </c>
@@ -16426,7 +15790,7 @@
       <c r="S300" s="21"/>
       <c r="T300" s="21"/>
     </row>
-    <row r="301" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="18" t="s">
         <v>270</v>
       </c>
@@ -16483,7 +15847,7 @@
       <c r="S301" s="21"/>
       <c r="T301" s="21"/>
     </row>
-    <row r="302" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="18" t="s">
         <v>270</v>
       </c>
@@ -16540,7 +15904,7 @@
       <c r="S302" s="21"/>
       <c r="T302" s="21"/>
     </row>
-    <row r="303" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="18" t="s">
         <v>270</v>
       </c>
@@ -16597,7 +15961,7 @@
       <c r="S303" s="21"/>
       <c r="T303" s="21"/>
     </row>
-    <row r="304" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="18" t="s">
         <v>270</v>
       </c>
@@ -16654,7 +16018,7 @@
       <c r="S304" s="21"/>
       <c r="T304" s="21"/>
     </row>
-    <row r="305" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="18" t="s">
         <v>270</v>
       </c>
@@ -16711,7 +16075,7 @@
       <c r="S305" s="21"/>
       <c r="T305" s="21"/>
     </row>
-    <row r="306" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="18" t="s">
         <v>270</v>
       </c>
@@ -16768,7 +16132,7 @@
       <c r="S306" s="21"/>
       <c r="T306" s="21"/>
     </row>
-    <row r="307" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="18" t="s">
         <v>270</v>
       </c>
@@ -16825,7 +16189,7 @@
       <c r="S307" s="21"/>
       <c r="T307" s="21"/>
     </row>
-    <row r="308" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="18" t="s">
         <v>270</v>
       </c>
@@ -16882,7 +16246,7 @@
       <c r="S308" s="21"/>
       <c r="T308" s="21"/>
     </row>
-    <row r="309" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="18" t="s">
         <v>270</v>
       </c>
@@ -16939,7 +16303,7 @@
       <c r="S309" s="21"/>
       <c r="T309" s="21"/>
     </row>
-    <row r="310" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="18" t="s">
         <v>270</v>
       </c>
@@ -16996,7 +16360,7 @@
       <c r="S310" s="21"/>
       <c r="T310" s="21"/>
     </row>
-    <row r="311" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="18" t="s">
         <v>270</v>
       </c>
@@ -17053,7 +16417,7 @@
       <c r="S311" s="21"/>
       <c r="T311" s="21"/>
     </row>
-    <row r="312" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="18" t="s">
         <v>270</v>
       </c>
@@ -17110,7 +16474,7 @@
       <c r="S312" s="21"/>
       <c r="T312" s="21"/>
     </row>
-    <row r="313" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="18" t="s">
         <v>270</v>
       </c>
@@ -17167,7 +16531,7 @@
       <c r="S313" s="21"/>
       <c r="T313" s="21"/>
     </row>
-    <row r="314" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="18" t="s">
         <v>270</v>
       </c>
@@ -17224,7 +16588,7 @@
       <c r="S314" s="21"/>
       <c r="T314" s="21"/>
     </row>
-    <row r="315" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="18" t="s">
         <v>270</v>
       </c>
@@ -17281,7 +16645,7 @@
       <c r="S315" s="21"/>
       <c r="T315" s="21"/>
     </row>
-    <row r="316" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="18" t="s">
         <v>270</v>
       </c>
@@ -17338,7 +16702,7 @@
       <c r="S316" s="21"/>
       <c r="T316" s="21"/>
     </row>
-    <row r="317" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="18" t="s">
         <v>270</v>
       </c>
@@ -17395,7 +16759,7 @@
       <c r="S317" s="21"/>
       <c r="T317" s="21"/>
     </row>
-    <row r="318" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="18" t="s">
         <v>270</v>
       </c>
@@ -17452,7 +16816,7 @@
       <c r="S318" s="21"/>
       <c r="T318" s="21"/>
     </row>
-    <row r="319" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="18" t="s">
         <v>270</v>
       </c>
@@ -17509,7 +16873,7 @@
       <c r="S319" s="21"/>
       <c r="T319" s="21"/>
     </row>
-    <row r="320" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="18" t="s">
         <v>270</v>
       </c>
@@ -17566,7 +16930,7 @@
       <c r="S320" s="21"/>
       <c r="T320" s="21"/>
     </row>
-    <row r="321" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="18" t="s">
         <v>270</v>
       </c>
@@ -17623,7 +16987,7 @@
       <c r="S321" s="21"/>
       <c r="T321" s="21"/>
     </row>
-    <row r="322" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="18" t="s">
         <v>270</v>
       </c>
@@ -17680,7 +17044,7 @@
       <c r="S322" s="21"/>
       <c r="T322" s="21"/>
     </row>
-    <row r="323" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="18" t="s">
         <v>270</v>
       </c>
@@ -17737,7 +17101,7 @@
       <c r="S323" s="21"/>
       <c r="T323" s="21"/>
     </row>
-    <row r="324" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="18" t="s">
         <v>270</v>
       </c>
@@ -17794,7 +17158,7 @@
       <c r="S324" s="21"/>
       <c r="T324" s="21"/>
     </row>
-    <row r="325" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="18" t="s">
         <v>270</v>
       </c>
@@ -17851,7 +17215,7 @@
       <c r="S325" s="21"/>
       <c r="T325" s="21"/>
     </row>
-    <row r="326" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="18" t="s">
         <v>270</v>
       </c>
@@ -17908,7 +17272,7 @@
       <c r="S326" s="21"/>
       <c r="T326" s="21"/>
     </row>
-    <row r="327" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="18" t="s">
         <v>270</v>
       </c>
@@ -17965,7 +17329,7 @@
       <c r="S327" s="21"/>
       <c r="T327" s="21"/>
     </row>
-    <row r="328" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="18" t="s">
         <v>270</v>
       </c>
@@ -18022,7 +17386,7 @@
       <c r="S328" s="21"/>
       <c r="T328" s="21"/>
     </row>
-    <row r="329" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="18" t="s">
         <v>270</v>
       </c>
@@ -18079,7 +17443,7 @@
       <c r="S329" s="21"/>
       <c r="T329" s="21"/>
     </row>
-    <row r="330" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="18" t="s">
         <v>270</v>
       </c>
@@ -18136,7 +17500,7 @@
       <c r="S330" s="21"/>
       <c r="T330" s="21"/>
     </row>
-    <row r="331" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="18" t="s">
         <v>270</v>
       </c>
@@ -18193,7 +17557,7 @@
       <c r="S331" s="21"/>
       <c r="T331" s="21"/>
     </row>
-    <row r="332" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="18" t="s">
         <v>270</v>
       </c>
@@ -18250,7 +17614,7 @@
       <c r="S332" s="21"/>
       <c r="T332" s="21"/>
     </row>
-    <row r="333" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="18" t="s">
         <v>270</v>
       </c>
@@ -18307,7 +17671,7 @@
       <c r="S333" s="21"/>
       <c r="T333" s="21"/>
     </row>
-    <row r="334" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="18" t="s">
         <v>270</v>
       </c>
@@ -18364,7 +17728,7 @@
       <c r="S334" s="21"/>
       <c r="T334" s="21"/>
     </row>
-    <row r="335" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="18" t="s">
         <v>270</v>
       </c>
@@ -18421,7 +17785,7 @@
       <c r="S335" s="21"/>
       <c r="T335" s="21"/>
     </row>
-    <row r="336" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="18" t="s">
         <v>270</v>
       </c>
@@ -18478,7 +17842,7 @@
       <c r="S336" s="21"/>
       <c r="T336" s="21"/>
     </row>
-    <row r="337" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="18" t="s">
         <v>270</v>
       </c>
@@ -18535,7 +17899,7 @@
       <c r="S337" s="21"/>
       <c r="T337" s="21"/>
     </row>
-    <row r="338" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="18" t="s">
         <v>270</v>
       </c>
@@ -18592,7 +17956,7 @@
       <c r="S338" s="21"/>
       <c r="T338" s="21"/>
     </row>
-    <row r="339" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="18" t="s">
         <v>270</v>
       </c>
@@ -18649,7 +18013,7 @@
       <c r="S339" s="21"/>
       <c r="T339" s="21"/>
     </row>
-    <row r="340" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="18" t="s">
         <v>270</v>
       </c>
@@ -18706,7 +18070,7 @@
       <c r="S340" s="21"/>
       <c r="T340" s="21"/>
     </row>
-    <row r="341" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="18" t="s">
         <v>270</v>
       </c>
@@ -18763,7 +18127,7 @@
       <c r="S341" s="21"/>
       <c r="T341" s="21"/>
     </row>
-    <row r="342" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="18" t="s">
         <v>270</v>
       </c>
@@ -18820,7 +18184,7 @@
       <c r="S342" s="21"/>
       <c r="T342" s="21"/>
     </row>
-    <row r="343" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="18" t="s">
         <v>270</v>
       </c>
@@ -18877,7 +18241,7 @@
       <c r="S343" s="21"/>
       <c r="T343" s="21"/>
     </row>
-    <row r="344" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="18" t="s">
         <v>270</v>
       </c>
@@ -18934,7 +18298,7 @@
       <c r="S344" s="21"/>
       <c r="T344" s="21"/>
     </row>
-    <row r="345" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="18" t="s">
         <v>270</v>
       </c>
@@ -18991,7 +18355,7 @@
       <c r="S345" s="21"/>
       <c r="T345" s="21"/>
     </row>
-    <row r="346" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="18" t="s">
         <v>270</v>
       </c>
@@ -19048,7 +18412,7 @@
       <c r="S346" s="21"/>
       <c r="T346" s="21"/>
     </row>
-    <row r="347" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="18" t="s">
         <v>270</v>
       </c>
@@ -19105,7 +18469,7 @@
       <c r="S347" s="21"/>
       <c r="T347" s="21"/>
     </row>
-    <row r="348" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="18" t="s">
         <v>270</v>
       </c>
@@ -19162,7 +18526,7 @@
       <c r="S348" s="21"/>
       <c r="T348" s="21"/>
     </row>
-    <row r="349" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="18" t="s">
         <v>270</v>
       </c>
@@ -19219,7 +18583,7 @@
       <c r="S349" s="21"/>
       <c r="T349" s="21"/>
     </row>
-    <row r="350" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="18" t="s">
         <v>270</v>
       </c>
@@ -19276,7 +18640,7 @@
       <c r="S350" s="21"/>
       <c r="T350" s="21"/>
     </row>
-    <row r="351" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="18" t="s">
         <v>270</v>
       </c>
@@ -19333,7 +18697,7 @@
       <c r="S351" s="21"/>
       <c r="T351" s="21"/>
     </row>
-    <row r="352" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="18" t="s">
         <v>270</v>
       </c>
@@ -19390,7 +18754,7 @@
       <c r="S352" s="21"/>
       <c r="T352" s="21"/>
     </row>
-    <row r="353" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="18" t="s">
         <v>270</v>
       </c>
@@ -19447,7 +18811,7 @@
       <c r="S353" s="21"/>
       <c r="T353" s="21"/>
     </row>
-    <row r="354" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="18" t="s">
         <v>270</v>
       </c>
@@ -19504,7 +18868,7 @@
       <c r="S354" s="21"/>
       <c r="T354" s="21"/>
     </row>
-    <row r="355" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="18" t="s">
         <v>270</v>
       </c>
@@ -19561,7 +18925,7 @@
       <c r="S355" s="21"/>
       <c r="T355" s="21"/>
     </row>
-    <row r="356" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="18" t="s">
         <v>270</v>
       </c>
@@ -19618,7 +18982,7 @@
       <c r="S356" s="21"/>
       <c r="T356" s="21"/>
     </row>
-    <row r="357" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="18" t="s">
         <v>270</v>
       </c>
@@ -19675,7 +19039,7 @@
       <c r="S357" s="21"/>
       <c r="T357" s="21"/>
     </row>
-    <row r="358" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="18" t="s">
         <v>270</v>
       </c>
@@ -19732,7 +19096,7 @@
       <c r="S358" s="21"/>
       <c r="T358" s="21"/>
     </row>
-    <row r="359" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="18" t="s">
         <v>270</v>
       </c>
@@ -19789,7 +19153,7 @@
       <c r="S359" s="21"/>
       <c r="T359" s="21"/>
     </row>
-    <row r="360" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="18" t="s">
         <v>270</v>
       </c>
@@ -19846,7 +19210,7 @@
       <c r="S360" s="21"/>
       <c r="T360" s="21"/>
     </row>
-    <row r="361" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="18" t="s">
         <v>270</v>
       </c>
@@ -19903,7 +19267,7 @@
       <c r="S361" s="21"/>
       <c r="T361" s="21"/>
     </row>
-    <row r="362" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="18" t="s">
         <v>270</v>
       </c>
@@ -19960,7 +19324,7 @@
       <c r="S362" s="21"/>
       <c r="T362" s="21"/>
     </row>
-    <row r="363" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="18" t="s">
         <v>270</v>
       </c>
@@ -20017,7 +19381,7 @@
       <c r="S363" s="21"/>
       <c r="T363" s="21"/>
     </row>
-    <row r="364" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="18" t="s">
         <v>270</v>
       </c>
@@ -20074,7 +19438,7 @@
       <c r="S364" s="21"/>
       <c r="T364" s="21"/>
     </row>
-    <row r="365" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="18" t="s">
         <v>270</v>
       </c>
@@ -20131,7 +19495,7 @@
       <c r="S365" s="21"/>
       <c r="T365" s="21"/>
     </row>
-    <row r="366" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="18" t="s">
         <v>270</v>
       </c>
@@ -20188,7 +19552,7 @@
       <c r="S366" s="21"/>
       <c r="T366" s="21"/>
     </row>
-    <row r="367" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="18" t="s">
         <v>270</v>
       </c>
@@ -20245,7 +19609,7 @@
       <c r="S367" s="21"/>
       <c r="T367" s="21"/>
     </row>
-    <row r="368" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="18" t="s">
         <v>270</v>
       </c>
@@ -20302,7 +19666,7 @@
       <c r="S368" s="21"/>
       <c r="T368" s="21"/>
     </row>
-    <row r="369" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="18" t="s">
         <v>270</v>
       </c>
@@ -20359,7 +19723,7 @@
       <c r="S369" s="21"/>
       <c r="T369" s="21"/>
     </row>
-    <row r="370" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="18" t="s">
         <v>270</v>
       </c>
@@ -20416,7 +19780,7 @@
       <c r="S370" s="21"/>
       <c r="T370" s="21"/>
     </row>
-    <row r="371" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="18" t="s">
         <v>270</v>
       </c>
@@ -20473,7 +19837,7 @@
       <c r="S371" s="21"/>
       <c r="T371" s="21"/>
     </row>
-    <row r="372" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="18" t="s">
         <v>270</v>
       </c>
@@ -20530,7 +19894,7 @@
       <c r="S372" s="21"/>
       <c r="T372" s="21"/>
     </row>
-    <row r="373" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="18" t="s">
         <v>270</v>
       </c>
@@ -20587,7 +19951,7 @@
       <c r="S373" s="21"/>
       <c r="T373" s="21"/>
     </row>
-    <row r="374" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="18" t="s">
         <v>270</v>
       </c>
@@ -20644,7 +20008,7 @@
       <c r="S374" s="21"/>
       <c r="T374" s="21"/>
     </row>
-    <row r="375" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="18" t="s">
         <v>270</v>
       </c>
@@ -20701,7 +20065,7 @@
       <c r="S375" s="21"/>
       <c r="T375" s="21"/>
     </row>
-    <row r="376" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="18" t="s">
         <v>270</v>
       </c>
@@ -20758,7 +20122,7 @@
       <c r="S376" s="21"/>
       <c r="T376" s="21"/>
     </row>
-    <row r="377" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="18" t="s">
         <v>270</v>
       </c>
@@ -20815,7 +20179,7 @@
       <c r="S377" s="21"/>
       <c r="T377" s="21"/>
     </row>
-    <row r="378" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="18" t="s">
         <v>270</v>
       </c>
@@ -20872,7 +20236,7 @@
       <c r="S378" s="21"/>
       <c r="T378" s="21"/>
     </row>
-    <row r="379" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="18" t="s">
         <v>270</v>
       </c>
@@ -20929,7 +20293,7 @@
       <c r="S379" s="21"/>
       <c r="T379" s="21"/>
     </row>
-    <row r="380" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="18" t="s">
         <v>270</v>
       </c>
@@ -20986,7 +20350,7 @@
       <c r="S380" s="21"/>
       <c r="T380" s="21"/>
     </row>
-    <row r="381" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="18" t="s">
         <v>270</v>
       </c>
@@ -21043,7 +20407,7 @@
       <c r="S381" s="21"/>
       <c r="T381" s="21"/>
     </row>
-    <row r="382" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="18" t="s">
         <v>270</v>
       </c>
@@ -21100,7 +20464,7 @@
       <c r="S382" s="21"/>
       <c r="T382" s="21"/>
     </row>
-    <row r="383" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="18" t="s">
         <v>270</v>
       </c>
@@ -21157,7 +20521,7 @@
       <c r="S383" s="21"/>
       <c r="T383" s="21"/>
     </row>
-    <row r="384" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="18" t="s">
         <v>270</v>
       </c>
@@ -21214,7 +20578,7 @@
       <c r="S384" s="21"/>
       <c r="T384" s="21"/>
     </row>
-    <row r="385" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="18" t="s">
         <v>270</v>
       </c>
@@ -21271,7 +20635,7 @@
       <c r="S385" s="21"/>
       <c r="T385" s="21"/>
     </row>
-    <row r="386" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="18" t="s">
         <v>270</v>
       </c>
@@ -21328,7 +20692,7 @@
       <c r="S386" s="21"/>
       <c r="T386" s="21"/>
     </row>
-    <row r="387" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="18" t="s">
         <v>270</v>
       </c>
@@ -21385,7 +20749,7 @@
       <c r="S387" s="21"/>
       <c r="T387" s="21"/>
     </row>
-    <row r="388" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="18" t="s">
         <v>270</v>
       </c>
@@ -21442,7 +20806,7 @@
       <c r="S388" s="21"/>
       <c r="T388" s="21"/>
     </row>
-    <row r="389" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="18" t="s">
         <v>270</v>
       </c>
@@ -21499,7 +20863,7 @@
       <c r="S389" s="21"/>
       <c r="T389" s="21"/>
     </row>
-    <row r="390" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="18" t="s">
         <v>270</v>
       </c>
@@ -21556,7 +20920,7 @@
       <c r="S390" s="21"/>
       <c r="T390" s="21"/>
     </row>
-    <row r="391" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="18" t="s">
         <v>270</v>
       </c>
@@ -21613,7 +20977,7 @@
       <c r="S391" s="21"/>
       <c r="T391" s="21"/>
     </row>
-    <row r="392" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="18" t="s">
         <v>270</v>
       </c>
@@ -21670,7 +21034,7 @@
       <c r="S392" s="21"/>
       <c r="T392" s="21"/>
     </row>
-    <row r="393" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="18" t="s">
         <v>270</v>
       </c>
@@ -21727,7 +21091,7 @@
       <c r="S393" s="21"/>
       <c r="T393" s="21"/>
     </row>
-    <row r="394" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="18" t="s">
         <v>270</v>
       </c>
@@ -21784,7 +21148,7 @@
       <c r="S394" s="21"/>
       <c r="T394" s="21"/>
     </row>
-    <row r="395" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="18" t="s">
         <v>270</v>
       </c>
@@ -21841,7 +21205,7 @@
       <c r="S395" s="21"/>
       <c r="T395" s="21"/>
     </row>
-    <row r="396" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="18" t="s">
         <v>270</v>
       </c>
@@ -21898,7 +21262,7 @@
       <c r="S396" s="21"/>
       <c r="T396" s="21"/>
     </row>
-    <row r="397" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="18" t="s">
         <v>270</v>
       </c>
@@ -21955,7 +21319,7 @@
       <c r="S397" s="21"/>
       <c r="T397" s="21"/>
     </row>
-    <row r="398" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="18" t="s">
         <v>270</v>
       </c>
@@ -22012,7 +21376,7 @@
       <c r="S398" s="21"/>
       <c r="T398" s="21"/>
     </row>
-    <row r="399" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="18" t="s">
         <v>270</v>
       </c>
@@ -22069,7 +21433,7 @@
       <c r="S399" s="21"/>
       <c r="T399" s="21"/>
     </row>
-    <row r="400" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="18" t="s">
         <v>270</v>
       </c>
@@ -22126,7 +21490,7 @@
       <c r="S400" s="21"/>
       <c r="T400" s="21"/>
     </row>
-    <row r="401" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="18" t="s">
         <v>270</v>
       </c>
@@ -22183,7 +21547,7 @@
       <c r="S401" s="21"/>
       <c r="T401" s="21"/>
     </row>
-    <row r="402" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="18" t="s">
         <v>270</v>
       </c>
@@ -22240,7 +21604,7 @@
       <c r="S402" s="21"/>
       <c r="T402" s="21"/>
     </row>
-    <row r="403" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="18" t="s">
         <v>270</v>
       </c>
@@ -22297,7 +21661,7 @@
       <c r="S403" s="21"/>
       <c r="T403" s="21"/>
     </row>
-    <row r="404" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="18" t="s">
         <v>270</v>
       </c>
@@ -22354,7 +21718,7 @@
       <c r="S404" s="21"/>
       <c r="T404" s="21"/>
     </row>
-    <row r="405" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="18" t="s">
         <v>270</v>
       </c>
@@ -22411,7 +21775,7 @@
       <c r="S405" s="21"/>
       <c r="T405" s="21"/>
     </row>
-    <row r="406" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="18" t="s">
         <v>270</v>
       </c>
@@ -22468,7 +21832,7 @@
       <c r="S406" s="21"/>
       <c r="T406" s="21"/>
     </row>
-    <row r="407" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="18" t="s">
         <v>270</v>
       </c>
@@ -22525,7 +21889,7 @@
       <c r="S407" s="21"/>
       <c r="T407" s="21"/>
     </row>
-    <row r="408" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="18" t="s">
         <v>270</v>
       </c>
@@ -22582,7 +21946,7 @@
       <c r="S408" s="21"/>
       <c r="T408" s="21"/>
     </row>
-    <row r="409" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="18" t="s">
         <v>270</v>
       </c>
@@ -22639,7 +22003,7 @@
       <c r="S409" s="21"/>
       <c r="T409" s="21"/>
     </row>
-    <row r="410" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="18" t="s">
         <v>270</v>
       </c>
@@ -22696,7 +22060,7 @@
       <c r="S410" s="21"/>
       <c r="T410" s="21"/>
     </row>
-    <row r="411" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="18" t="s">
         <v>270</v>
       </c>
@@ -22753,7 +22117,7 @@
       <c r="S411" s="21"/>
       <c r="T411" s="21"/>
     </row>
-    <row r="412" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="18" t="s">
         <v>270</v>
       </c>
@@ -22810,7 +22174,7 @@
       <c r="S412" s="21"/>
       <c r="T412" s="21"/>
     </row>
-    <row r="413" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="18" t="s">
         <v>270</v>
       </c>
@@ -22867,7 +22231,7 @@
       <c r="S413" s="21"/>
       <c r="T413" s="21"/>
     </row>
-    <row r="414" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="18" t="s">
         <v>270</v>
       </c>
@@ -22924,7 +22288,7 @@
       <c r="S414" s="21"/>
       <c r="T414" s="21"/>
     </row>
-    <row r="415" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="18" t="s">
         <v>270</v>
       </c>
@@ -22981,7 +22345,7 @@
       <c r="S415" s="21"/>
       <c r="T415" s="21"/>
     </row>
-    <row r="416" customFormat="false" ht="114" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="18" t="s">
         <v>270</v>
       </c>
@@ -23038,7 +22402,7 @@
       <c r="S416" s="21"/>
       <c r="T416" s="21"/>
     </row>
-    <row r="417" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="18" t="s">
         <v>270</v>
       </c>
@@ -23095,7 +22459,7 @@
       <c r="S417" s="21"/>
       <c r="T417" s="21"/>
     </row>
-    <row r="418" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="18" t="s">
         <v>270</v>
       </c>
